--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -23693,10 +23693,10 @@
         <v>39</v>
       </c>
       <c r="H629" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="I629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630">
@@ -23721,13 +23721,13 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F630" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G630" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H630" t="n">
         <v>950</v>
@@ -24211,10 +24211,10 @@
         <v>96</v>
       </c>
       <c r="H643" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I643" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -24581,10 +24581,10 @@
         <v>36</v>
       </c>
       <c r="H653" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654">
@@ -26320,10 +26320,10 @@
         <v>19</v>
       </c>
       <c r="H700" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="701">

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -23314,13 +23314,13 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F619" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G619" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H619" t="n">
         <v>451</v>
@@ -23351,13 +23351,13 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F620" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G620" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H620" t="n">
         <v>226</v>
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F621" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G621" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H621" t="n">
         <v>0</v>
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F623" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G623" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -23499,13 +23499,13 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F624" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G624" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H624" t="n">
         <v>253</v>
@@ -23536,13 +23536,13 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F625" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G625" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H625" t="n">
         <v>51</v>
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F627" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G627" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H627" t="n">
         <v>202</v>
@@ -23647,13 +23647,13 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F628" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="G628" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H628" t="n">
         <v>7437</v>
@@ -23684,13 +23684,13 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F629" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G629" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H629" t="n">
         <v>89</v>
@@ -23721,13 +23721,13 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F630" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G630" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H630" t="n">
         <v>950</v>
@@ -23832,13 +23832,13 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -23943,13 +23943,13 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F636" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G636" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H636" t="n">
         <v>1117</v>
@@ -24091,13 +24091,13 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F640" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G640" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H640" t="n">
         <v>14079</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F643" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G643" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H643" t="n">
         <v>84</v>
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F645" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G645" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -24350,13 +24350,13 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F647" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G647" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -24424,13 +24424,13 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F649" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G649" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -24461,13 +24461,13 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F650" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G650" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H650" t="n">
         <v>320</v>
@@ -24498,13 +24498,13 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F651" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G651" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H651" t="n">
         <v>55</v>
@@ -24535,13 +24535,13 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F652" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G652" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H652" t="n">
         <v>0</v>
@@ -24609,13 +24609,13 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F654" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G654" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -24683,13 +24683,13 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F656" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G656" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -24757,13 +24757,13 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F658" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G658" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F659" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G659" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H659" t="n">
         <v>52</v>
@@ -24942,13 +24942,13 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F663" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G663" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H663" t="n">
         <v>14</v>
@@ -24979,13 +24979,13 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F664" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G664" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H664" t="n">
         <v>72</v>
@@ -25127,13 +25127,13 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F668" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G668" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H668" t="n">
         <v>193</v>
@@ -25608,13 +25608,13 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F681" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G681" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -25645,13 +25645,13 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F682" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G682" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -25719,13 +25719,13 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F684" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G684" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H684" t="n">
         <v>24</v>
@@ -25756,13 +25756,13 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F685" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G685" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F687" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G687" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -25867,13 +25867,13 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F688" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G688" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -25904,13 +25904,13 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F689" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G689" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25978,13 +25978,13 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F691" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G691" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -26052,13 +26052,13 @@
         </is>
       </c>
       <c r="E693" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F693" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -26274,13 +26274,13 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F699" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G699" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I728"/>
+  <dimension ref="A1:I729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16959,10 +16959,10 @@
         <v>21</v>
       </c>
       <c r="H447" t="n">
-        <v>847</v>
+        <v>956</v>
       </c>
       <c r="I447" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="448">
@@ -17773,10 +17773,10 @@
         <v>7</v>
       </c>
       <c r="H469" t="n">
-        <v>3480</v>
+        <v>3372</v>
       </c>
       <c r="I469" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="470">
@@ -19475,10 +19475,10 @@
         <v>15</v>
       </c>
       <c r="H515" t="n">
-        <v>8575</v>
+        <v>8650</v>
       </c>
       <c r="I515" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="516">
@@ -19549,10 +19549,10 @@
         <v>134</v>
       </c>
       <c r="H517" t="n">
-        <v>7490</v>
+        <v>7520</v>
       </c>
       <c r="I517" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="518">
@@ -19956,10 +19956,10 @@
         <v>24</v>
       </c>
       <c r="H528" t="n">
-        <v>741</v>
+        <v>765</v>
       </c>
       <c r="I528" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="529">
@@ -23314,19 +23314,19 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F619" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G619" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H619" t="n">
-        <v>451</v>
+        <v>577</v>
       </c>
       <c r="I619" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="620">
@@ -23471,10 +23471,10 @@
         <v>28</v>
       </c>
       <c r="H623" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624">
@@ -23573,19 +23573,19 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F626" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G626" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H626" t="n">
-        <v>9431</v>
+        <v>10435</v>
       </c>
       <c r="I626" t="n">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
     <row r="627">
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F627" t="n">
+        <v>100</v>
+      </c>
+      <c r="G627" t="n">
         <v>101</v>
-      </c>
-      <c r="G627" t="n">
-        <v>102</v>
       </c>
       <c r="H627" t="n">
         <v>202</v>
@@ -23656,10 +23656,10 @@
         <v>253</v>
       </c>
       <c r="H628" t="n">
-        <v>7437</v>
+        <v>7979</v>
       </c>
       <c r="I628" t="n">
-        <v>298</v>
+        <v>327</v>
       </c>
     </row>
     <row r="629">
@@ -23693,10 +23693,10 @@
         <v>42</v>
       </c>
       <c r="H629" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I629" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="630">
@@ -23804,10 +23804,10 @@
         <v>11</v>
       </c>
       <c r="H632" t="n">
-        <v>490</v>
+        <v>581</v>
       </c>
       <c r="I632" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="633">
@@ -23943,19 +23943,19 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F636" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G636" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H636" t="n">
-        <v>1117</v>
+        <v>1217</v>
       </c>
       <c r="I636" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="637">
@@ -24026,10 +24026,10 @@
         <v>2</v>
       </c>
       <c r="H638" t="n">
-        <v>5081</v>
+        <v>5432</v>
       </c>
       <c r="I638" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
     </row>
     <row r="639">
@@ -24063,10 +24063,10 @@
         <v>17</v>
       </c>
       <c r="H639" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="I639" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="640">
@@ -24100,10 +24100,10 @@
         <v>41</v>
       </c>
       <c r="H640" t="n">
-        <v>14079</v>
+        <v>14789</v>
       </c>
       <c r="I640" t="n">
-        <v>521</v>
+        <v>548</v>
       </c>
     </row>
     <row r="641">
@@ -24137,10 +24137,10 @@
         <v>0</v>
       </c>
       <c r="H641" t="n">
-        <v>1424</v>
+        <v>1553</v>
       </c>
       <c r="I641" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="642">
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F643" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G643" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H643" t="n">
         <v>84</v>
@@ -24248,10 +24248,10 @@
         <v>7</v>
       </c>
       <c r="H644" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I644" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -24433,10 +24433,10 @@
         <v>4</v>
       </c>
       <c r="H649" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -24470,10 +24470,10 @@
         <v>21</v>
       </c>
       <c r="H650" t="n">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="I650" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="651">
@@ -24507,10 +24507,10 @@
         <v>45</v>
       </c>
       <c r="H651" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="I651" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="652">
@@ -24535,13 +24535,13 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F652" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G652" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H652" t="n">
         <v>0</v>
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F659" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G659" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H659" t="n">
         <v>52</v>
@@ -24942,13 +24942,13 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F663" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G663" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H663" t="n">
         <v>14</v>
@@ -25571,13 +25571,13 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F680" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G680" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -25719,19 +25719,19 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F684" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G684" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H684" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -25950,10 +25950,10 @@
         <v>33</v>
       </c>
       <c r="H690" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I690" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="691">
@@ -26061,10 +26061,10 @@
         <v>6</v>
       </c>
       <c r="H693" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694">
@@ -26320,10 +26320,10 @@
         <v>19</v>
       </c>
       <c r="H700" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I700" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="701">
@@ -26508,7 +26508,7 @@
         <v>108</v>
       </c>
       <c r="I705" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="706">
@@ -26542,10 +26542,10 @@
         <v>18</v>
       </c>
       <c r="H706" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="I706" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="707">
@@ -27134,10 +27134,10 @@
         <v>16</v>
       </c>
       <c r="H722" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="I722" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="723">
@@ -27190,22 +27190,22 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F724" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G724" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -27232,7 +27232,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E725" t="n">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -27282,10 +27282,10 @@
         <v>1</v>
       </c>
       <c r="H726" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I726" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
@@ -27301,12 +27301,12 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E727" t="n">
@@ -27319,10 +27319,10 @@
         <v>1</v>
       </c>
       <c r="H727" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I727" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="728">
@@ -27343,22 +27343,59 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E728" t="n">
+        <v>1</v>
+      </c>
+      <c r="F728" t="n">
+        <v>1</v>
+      </c>
+      <c r="G728" t="n">
+        <v>1</v>
+      </c>
+      <c r="H728" t="n">
+        <v>0</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
         <v>2</v>
       </c>
-      <c r="F728" t="n">
+      <c r="F729" t="n">
         <v>2</v>
       </c>
-      <c r="G728" t="n">
+      <c r="G729" t="n">
         <v>2</v>
       </c>
-      <c r="H728" t="n">
-        <v>0</v>
-      </c>
-      <c r="I728" t="n">
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+      <c r="I729" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -10364,13 +10364,13 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F269" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G269" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H269" t="n">
         <v>9188</v>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F281" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G281" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H281" t="n">
         <v>32829</v>
@@ -17024,19 +17024,19 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F449" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G449" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H449" t="n">
-        <v>3802</v>
+        <v>3862</v>
       </c>
       <c r="I449" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="450">
@@ -17320,19 +17320,19 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F457" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G457" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H457" t="n">
-        <v>1914</v>
+        <v>1854</v>
       </c>
       <c r="I457" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="458">
@@ -19475,10 +19475,10 @@
         <v>15</v>
       </c>
       <c r="H515" t="n">
-        <v>8650</v>
+        <v>8679</v>
       </c>
       <c r="I515" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="516">
@@ -19549,10 +19549,10 @@
         <v>134</v>
       </c>
       <c r="H517" t="n">
-        <v>7520</v>
+        <v>7620</v>
       </c>
       <c r="I517" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="518">
@@ -19845,10 +19845,10 @@
         <v>88</v>
       </c>
       <c r="H525" t="n">
-        <v>1842</v>
+        <v>1757</v>
       </c>
       <c r="I525" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="526">
@@ -19993,10 +19993,10 @@
         <v>30</v>
       </c>
       <c r="H529" t="n">
-        <v>7456</v>
+        <v>7476</v>
       </c>
       <c r="I529" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="530">
@@ -21029,10 +21029,10 @@
         <v>7</v>
       </c>
       <c r="H557" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="I557" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="558">
@@ -23286,10 +23286,10 @@
         <v>0</v>
       </c>
       <c r="H618" t="n">
-        <v>1180</v>
+        <v>1235</v>
       </c>
       <c r="I618" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="619">
@@ -23314,19 +23314,19 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F619" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G619" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H619" t="n">
-        <v>577</v>
+        <v>703</v>
       </c>
       <c r="I619" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="620">
@@ -23434,10 +23434,10 @@
         <v>3</v>
       </c>
       <c r="H622" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I622" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="623">
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F623" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G623" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H623" t="n">
         <v>46</v>
@@ -23499,13 +23499,13 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F624" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G624" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H624" t="n">
         <v>253</v>
@@ -23582,10 +23582,10 @@
         <v>30</v>
       </c>
       <c r="H626" t="n">
-        <v>10435</v>
+        <v>10980</v>
       </c>
       <c r="I626" t="n">
-        <v>420</v>
+        <v>445</v>
       </c>
     </row>
     <row r="627">
@@ -23610,19 +23610,19 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F627" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G627" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H627" t="n">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="I627" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="628">
@@ -23647,19 +23647,19 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F628" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G628" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H628" t="n">
-        <v>7979</v>
+        <v>8695</v>
       </c>
       <c r="I628" t="n">
-        <v>327</v>
+        <v>364</v>
       </c>
     </row>
     <row r="629">
@@ -23684,19 +23684,19 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F629" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G629" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H629" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="I629" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="630">
@@ -23730,10 +23730,10 @@
         <v>51</v>
       </c>
       <c r="H630" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="I630" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="631">
@@ -23767,10 +23767,10 @@
         <v>4</v>
       </c>
       <c r="H631" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632">
@@ -23869,19 +23869,19 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F634" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G634" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H634" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I634" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -23915,10 +23915,10 @@
         <v>40</v>
       </c>
       <c r="H635" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="I635" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="636">
@@ -23943,13 +23943,13 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F636" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G636" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H636" t="n">
         <v>1217</v>
@@ -24026,10 +24026,10 @@
         <v>2</v>
       </c>
       <c r="H638" t="n">
-        <v>5432</v>
+        <v>5676</v>
       </c>
       <c r="I638" t="n">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="639">
@@ -24100,10 +24100,10 @@
         <v>41</v>
       </c>
       <c r="H640" t="n">
-        <v>14789</v>
+        <v>15426</v>
       </c>
       <c r="I640" t="n">
-        <v>548</v>
+        <v>571</v>
       </c>
     </row>
     <row r="641">
@@ -24137,10 +24137,10 @@
         <v>0</v>
       </c>
       <c r="H641" t="n">
-        <v>1553</v>
+        <v>1654</v>
       </c>
       <c r="I641" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="642">
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F643" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G643" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H643" t="n">
         <v>84</v>
@@ -24498,19 +24498,19 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F651" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G651" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H651" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="I651" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="652">
@@ -24535,13 +24535,13 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F652" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G652" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H652" t="n">
         <v>0</v>
@@ -24572,13 +24572,13 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F653" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G653" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H653" t="n">
         <v>0</v>
@@ -24655,10 +24655,10 @@
         <v>8</v>
       </c>
       <c r="H655" t="n">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="I655" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="656">
@@ -24692,10 +24692,10 @@
         <v>9</v>
       </c>
       <c r="H656" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657">
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F659" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G659" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H659" t="n">
         <v>52</v>
@@ -24905,13 +24905,13 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F662" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G662" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -25395,10 +25395,10 @@
         <v>14</v>
       </c>
       <c r="H675" t="n">
-        <v>239</v>
+        <v>356</v>
       </c>
       <c r="I675" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="676">
@@ -25571,13 +25571,13 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F680" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G680" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -25645,13 +25645,13 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F682" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G682" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F687" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G687" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -25867,13 +25867,13 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F688" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G688" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -25904,13 +25904,13 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F689" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G689" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25941,13 +25941,13 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F690" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G690" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H690" t="n">
         <v>39</v>
@@ -26061,10 +26061,10 @@
         <v>6</v>
       </c>
       <c r="H693" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I693" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="694">
@@ -26163,13 +26163,13 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F696" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G696" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26320,10 +26320,10 @@
         <v>19</v>
       </c>
       <c r="H700" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I700" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="701">
@@ -26496,13 +26496,13 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H705" t="n">
         <v>108</v>
@@ -26542,10 +26542,10 @@
         <v>18</v>
       </c>
       <c r="H706" t="n">
-        <v>173</v>
+        <v>22</v>
       </c>
       <c r="I706" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707">
@@ -26949,10 +26949,10 @@
         <v>1</v>
       </c>
       <c r="H717" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="718">
@@ -27134,10 +27134,10 @@
         <v>16</v>
       </c>
       <c r="H722" t="n">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="I722" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="723">

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I729"/>
+  <dimension ref="A1:I731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
         <v>125</v>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H20" t="n">
         <v>1384</v>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22" t="n">
         <v>556</v>
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" t="n">
         <v>25</v>
@@ -2076,19 +2076,19 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>31</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31</v>
+      </c>
+      <c r="G45" t="n">
+        <v>31</v>
+      </c>
+      <c r="H45" t="n">
+        <v>706</v>
+      </c>
+      <c r="I45" t="n">
         <v>30</v>
-      </c>
-      <c r="F45" t="n">
-        <v>30</v>
-      </c>
-      <c r="G45" t="n">
-        <v>30</v>
-      </c>
-      <c r="H45" t="n">
-        <v>666</v>
-      </c>
-      <c r="I45" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -2298,19 +2298,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G71" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H71" t="n">
         <v>3149</v>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -5452,10 +5452,10 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="I136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -5822,10 +5822,10 @@
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -7228,10 +7228,10 @@
         <v>14</v>
       </c>
       <c r="H184" t="n">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="I184" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -7709,10 +7709,10 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="I197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -7820,10 +7820,10 @@
         <v>109</v>
       </c>
       <c r="H200" t="n">
-        <v>803</v>
+        <v>869</v>
       </c>
       <c r="I200" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="201">
@@ -8079,10 +8079,10 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="I207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208">
@@ -10142,13 +10142,13 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F263" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G263" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H263" t="n">
         <v>665</v>
@@ -10216,13 +10216,13 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F265" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G265" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H265" t="n">
         <v>3065</v>
@@ -10364,13 +10364,13 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F269" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G269" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H269" t="n">
         <v>9188</v>
@@ -10512,19 +10512,19 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H273" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -10734,19 +10734,19 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G279" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H279" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="I279" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F281" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G281" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H281" t="n">
         <v>32829</v>
@@ -12806,13 +12806,13 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F335" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G335" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H335" t="n">
         <v>3507</v>
@@ -13102,13 +13102,13 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F343" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G343" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H343" t="n">
         <v>393</v>
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F388" t="n">
         <v>187</v>
@@ -14878,13 +14878,13 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F391" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G391" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H391" t="n">
         <v>1789</v>
@@ -15063,13 +15063,13 @@
         </is>
       </c>
       <c r="E396" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F396" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G396" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H396" t="n">
         <v>338</v>
@@ -15100,13 +15100,13 @@
         </is>
       </c>
       <c r="E397" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F397" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G397" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H397" t="n">
         <v>435</v>
@@ -15214,10 +15214,10 @@
         <v>49</v>
       </c>
       <c r="F400" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G400" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H400" t="n">
         <v>191</v>
@@ -15581,13 +15581,13 @@
         </is>
       </c>
       <c r="E410" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F410" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G410" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -15655,13 +15655,13 @@
         </is>
       </c>
       <c r="E412" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F412" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G412" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H412" t="n">
         <v>64</v>
@@ -15803,13 +15803,13 @@
         </is>
       </c>
       <c r="E416" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F416" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G416" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -15840,13 +15840,13 @@
         </is>
       </c>
       <c r="E417" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F417" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G417" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -15951,13 +15951,13 @@
         </is>
       </c>
       <c r="E420" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F420" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G420" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H420" t="n">
         <v>25</v>
@@ -16136,13 +16136,13 @@
         </is>
       </c>
       <c r="E425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G425" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -16358,13 +16358,13 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -16802,19 +16802,19 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="F443" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="G443" t="n">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="H443" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="I443" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="444">
@@ -16876,19 +16876,19 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F445" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G445" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H445" t="n">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="I445" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="446">
@@ -16922,10 +16922,10 @@
         <v>10</v>
       </c>
       <c r="H446" t="n">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="I446" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="447">
@@ -17064,16 +17064,16 @@
         <v>129</v>
       </c>
       <c r="F450" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G450" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H450" t="n">
-        <v>13728</v>
+        <v>13779</v>
       </c>
       <c r="I450" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="451">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="E451" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F451" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G451" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H451" t="n">
         <v>1924</v>
@@ -17172,13 +17172,13 @@
         </is>
       </c>
       <c r="E453" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F453" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G453" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H453" t="n">
         <v>26</v>
@@ -17209,13 +17209,13 @@
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F454" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G454" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H454" t="n">
         <v>2756</v>
@@ -17246,13 +17246,13 @@
         </is>
       </c>
       <c r="E455" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F455" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G455" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H455" t="n">
         <v>322</v>
@@ -17292,10 +17292,10 @@
         <v>2</v>
       </c>
       <c r="H456" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="I456" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="457">
@@ -17320,19 +17320,19 @@
         </is>
       </c>
       <c r="E457" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F457" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G457" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H457" t="n">
-        <v>1854</v>
+        <v>1784</v>
       </c>
       <c r="I457" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="458">
@@ -17366,10 +17366,10 @@
         <v>65</v>
       </c>
       <c r="H458" t="n">
-        <v>4644</v>
+        <v>4620</v>
       </c>
       <c r="I458" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="459">
@@ -17431,13 +17431,13 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F460" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G460" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H460" t="n">
         <v>40833</v>
@@ -17468,13 +17468,13 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F461" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G461" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H461" t="n">
         <v>1514</v>
@@ -17508,16 +17508,16 @@
         <v>25</v>
       </c>
       <c r="F462" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G462" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H462" t="n">
-        <v>10992</v>
+        <v>10943</v>
       </c>
       <c r="I462" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="463">
@@ -17727,13 +17727,13 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F468" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G468" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H468" t="n">
         <v>49</v>
@@ -18097,13 +18097,13 @@
         </is>
       </c>
       <c r="E478" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F478" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G478" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H478" t="n">
         <v>0</v>
@@ -18726,13 +18726,13 @@
         </is>
       </c>
       <c r="E495" t="n">
+        <v>16</v>
+      </c>
+      <c r="F495" t="n">
         <v>17</v>
       </c>
-      <c r="F495" t="n">
-        <v>18</v>
-      </c>
       <c r="G495" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H495" t="n">
         <v>540</v>
@@ -18948,13 +18948,13 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F501" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G501" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H501" t="n">
         <v>647</v>
@@ -19179,10 +19179,10 @@
         <v>0</v>
       </c>
       <c r="H507" t="n">
-        <v>4516</v>
+        <v>4581</v>
       </c>
       <c r="I507" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="508">
@@ -19355,13 +19355,13 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F512" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G512" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H512" t="n">
         <v>185</v>
@@ -19475,10 +19475,10 @@
         <v>15</v>
       </c>
       <c r="H515" t="n">
-        <v>8679</v>
+        <v>9004</v>
       </c>
       <c r="I515" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="516">
@@ -19503,19 +19503,19 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F516" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G516" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H516" t="n">
-        <v>694</v>
+        <v>747</v>
       </c>
       <c r="I516" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="517">
@@ -19540,19 +19540,19 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F517" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G517" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H517" t="n">
-        <v>7620</v>
+        <v>7819</v>
       </c>
       <c r="I517" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="518">
@@ -19580,10 +19580,10 @@
         <v>224</v>
       </c>
       <c r="F518" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G518" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H518" t="n">
         <v>270</v>
@@ -19688,19 +19688,19 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F521" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G521" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H521" t="n">
-        <v>2307</v>
+        <v>2282</v>
       </c>
       <c r="I521" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="522">
@@ -19799,19 +19799,19 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F524" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G524" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H524" t="n">
-        <v>501</v>
+        <v>449</v>
       </c>
       <c r="I524" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="525">
@@ -19836,19 +19836,19 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F525" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G525" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H525" t="n">
-        <v>1757</v>
+        <v>1692</v>
       </c>
       <c r="I525" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="526">
@@ -19910,19 +19910,19 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H527" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="I527" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="528">
@@ -19984,13 +19984,13 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F529" t="n">
+        <v>28</v>
+      </c>
+      <c r="G529" t="n">
         <v>29</v>
-      </c>
-      <c r="G529" t="n">
-        <v>30</v>
       </c>
       <c r="H529" t="n">
         <v>7476</v>
@@ -21029,10 +21029,10 @@
         <v>7</v>
       </c>
       <c r="H557" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I557" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="558">
@@ -21362,10 +21362,10 @@
         <v>3</v>
       </c>
       <c r="H566" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="I566" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="567">
@@ -22759,19 +22759,19 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F604" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G604" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H604" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="I604" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="605">
@@ -23055,13 +23055,13 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F612" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G612" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H612" t="n">
         <v>68</v>
@@ -23268,7 +23268,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -23286,10 +23286,10 @@
         <v>0</v>
       </c>
       <c r="H618" t="n">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="I618" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619">
@@ -23300,33 +23300,33 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="F619" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G619" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="H619" t="n">
-        <v>703</v>
+        <v>1270</v>
       </c>
       <c r="I619" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="620">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -23351,19 +23351,19 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F620" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G620" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H620" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="I620" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="621">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -23388,19 +23388,19 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="F621" t="n">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="G621" t="n">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="H621" t="n">
-        <v>0</v>
+        <v>908</v>
       </c>
       <c r="I621" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="622">
@@ -23416,7 +23416,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -23425,19 +23425,19 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F622" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G622" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H622" t="n">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="I622" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="623">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -23462,19 +23462,19 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F623" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G623" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H623" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -23490,7 +23490,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -23499,19 +23499,19 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F624" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G624" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H624" t="n">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="I624" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="625">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -23536,19 +23536,19 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F625" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G625" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H625" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="I625" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626">
@@ -23564,7 +23564,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -23573,19 +23573,19 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F626" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G626" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H626" t="n">
-        <v>10980</v>
+        <v>310</v>
       </c>
       <c r="I626" t="n">
-        <v>445</v>
+        <v>11</v>
       </c>
     </row>
     <row r="627">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -23610,19 +23610,19 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="F627" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="G627" t="n">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="H627" t="n">
-        <v>394</v>
+        <v>51</v>
       </c>
       <c r="I627" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -23647,19 +23647,19 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="F628" t="n">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="G628" t="n">
-        <v>255</v>
+        <v>32</v>
       </c>
       <c r="H628" t="n">
-        <v>8695</v>
+        <v>13010</v>
       </c>
       <c r="I628" t="n">
-        <v>364</v>
+        <v>546</v>
       </c>
     </row>
     <row r="629">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -23684,19 +23684,19 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="F629" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="G629" t="n">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="H629" t="n">
-        <v>111</v>
+        <v>791</v>
       </c>
       <c r="I629" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="630">
@@ -23712,7 +23712,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -23721,19 +23721,19 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="F630" t="n">
-        <v>51</v>
+        <v>260</v>
       </c>
       <c r="G630" t="n">
-        <v>51</v>
+        <v>261</v>
       </c>
       <c r="H630" t="n">
-        <v>980</v>
+        <v>11279</v>
       </c>
       <c r="I630" t="n">
-        <v>37</v>
+        <v>553</v>
       </c>
     </row>
     <row r="631">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -23758,19 +23758,19 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="F631" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G631" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H631" t="n">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="I631" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="632">
@@ -23786,7 +23786,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -23795,19 +23795,19 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F632" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G632" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="H632" t="n">
-        <v>581</v>
+        <v>1159</v>
       </c>
       <c r="I632" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="633">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -23832,19 +23832,19 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F633" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G633" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H633" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="I633" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="634">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -23869,19 +23869,19 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F634" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G634" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H634" t="n">
-        <v>28</v>
+        <v>554</v>
       </c>
       <c r="I634" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="635">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -23906,19 +23906,19 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F635" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G635" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H635" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="I635" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -23943,19 +23943,19 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="F636" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="G636" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H636" t="n">
-        <v>1217</v>
+        <v>28</v>
       </c>
       <c r="I636" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -23971,7 +23971,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -23980,19 +23980,19 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F637" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="G637" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H637" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="I637" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="638">
@@ -24008,7 +24008,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -24017,19 +24017,19 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="G638" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H638" t="n">
-        <v>5676</v>
+        <v>1635</v>
       </c>
       <c r="I638" t="n">
-        <v>245</v>
+        <v>61</v>
       </c>
     </row>
     <row r="639">
@@ -24045,7 +24045,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -24054,19 +24054,19 @@
         </is>
       </c>
       <c r="E639" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F639" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G639" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H639" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="I639" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -24091,19 +24091,19 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F640" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G640" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H640" t="n">
-        <v>15426</v>
+        <v>6327</v>
       </c>
       <c r="I640" t="n">
-        <v>571</v>
+        <v>277</v>
       </c>
     </row>
     <row r="641">
@@ -24114,33 +24114,33 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F641" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G641" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H641" t="n">
-        <v>1654</v>
+        <v>240</v>
       </c>
       <c r="I641" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="642">
@@ -24151,12 +24151,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Ashwagandha Coffee</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -24165,19 +24165,19 @@
         </is>
       </c>
       <c r="E642" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F642" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G642" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H642" t="n">
-        <v>0</v>
+        <v>17477</v>
       </c>
       <c r="I642" t="n">
-        <v>0</v>
+        <v>657</v>
       </c>
     </row>
     <row r="643">
@@ -24188,33 +24188,33 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F643" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="G643" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="H643" t="n">
-        <v>84</v>
+        <v>2164</v>
       </c>
       <c r="I643" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="644">
@@ -24225,12 +24225,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Green Burner</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -24239,19 +24239,19 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F644" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G644" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H644" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I644" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -24276,19 +24276,19 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F645" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="G645" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="H645" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I645" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="646">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -24313,19 +24313,19 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F646" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G646" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H646" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I646" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="647">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -24350,13 +24350,13 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F647" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G647" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H647" t="n">
         <v>0</v>
@@ -24378,7 +24378,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -24387,13 +24387,13 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F648" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -24415,7 +24415,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -24424,19 +24424,19 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F649" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G649" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H649" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I649" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="650">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -24470,10 +24470,10 @@
         <v>21</v>
       </c>
       <c r="H650" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="I650" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="651">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -24498,19 +24498,19 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F651" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="G651" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H651" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="I651" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="652">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -24535,19 +24535,19 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="F652" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="G652" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="H652" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="I652" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="653">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -24572,19 +24572,19 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F653" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="G653" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="H653" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="I653" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="654">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -24609,13 +24609,13 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="F654" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="G654" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -24637,28 +24637,28 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F655" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="G655" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H655" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="I655" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -24674,28 +24674,28 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F656" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G656" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="H656" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">
@@ -24711,7 +24711,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -24729,10 +24729,10 @@
         <v>8</v>
       </c>
       <c r="H657" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="I657" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="658">
@@ -24748,7 +24748,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -24757,19 +24757,19 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F658" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G658" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="H658" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -24794,19 +24794,19 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F659" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G659" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H659" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I659" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -24831,19 +24831,19 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F660" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G660" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H660" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I660" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -24868,19 +24868,19 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="F661" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="G661" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="H661" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I661" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="662">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -24905,13 +24905,13 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F662" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G662" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -24942,19 +24942,19 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F663" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G663" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H663" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I663" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="664">
@@ -24965,12 +24965,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -24979,19 +24979,19 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F664" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G664" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H664" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I664" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
@@ -25002,12 +25002,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Hibiscus</t>
+          <t>Green Burner</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -25016,19 +25016,19 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F665" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G665" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H665" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
@@ -25044,28 +25044,28 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F666" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G666" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H666" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I666" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="667">
@@ -25081,28 +25081,28 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F667" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G667" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H667" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="I667" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668">
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -25127,19 +25127,19 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="F668" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G668" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H668" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="I668" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -25164,19 +25164,19 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F669" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G669" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H669" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="I669" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="670">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -25201,19 +25201,19 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F670" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G670" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="H670" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="I670" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="671">
@@ -25229,22 +25229,22 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H671" t="n">
         <v>0</v>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -25275,13 +25275,13 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F672" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G672" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -25303,22 +25303,22 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G673" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -25349,13 +25349,13 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F674" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G674" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -25377,28 +25377,28 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F675" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G675" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H675" t="n">
-        <v>356</v>
+        <v>30</v>
       </c>
       <c r="I675" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -25409,27 +25409,27 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="F676" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="G676" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -25446,12 +25446,12 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -25460,19 +25460,19 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F677" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G677" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H677" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="I677" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="678">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -25497,13 +25497,13 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="F678" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="G678" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -25525,12 +25525,12 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E679" t="n">
@@ -25557,12 +25557,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -25571,13 +25571,13 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F680" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G680" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H680" t="n">
         <v>0</v>
@@ -25594,27 +25594,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F681" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G681" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -25636,7 +25636,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -25645,19 +25645,19 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F682" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G682" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H682" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I682" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="683">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -25682,13 +25682,13 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F683" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G683" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -25719,19 +25719,19 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F684" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G684" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H684" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I684" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="685">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -25756,13 +25756,13 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F685" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G685" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -25793,19 +25793,19 @@
         </is>
       </c>
       <c r="E686" t="n">
+        <v>22</v>
+      </c>
+      <c r="F686" t="n">
+        <v>22</v>
+      </c>
+      <c r="G686" t="n">
+        <v>22</v>
+      </c>
+      <c r="H686" t="n">
+        <v>39</v>
+      </c>
+      <c r="I686" t="n">
         <v>2</v>
-      </c>
-      <c r="F686" t="n">
-        <v>2</v>
-      </c>
-      <c r="G686" t="n">
-        <v>2</v>
-      </c>
-      <c r="H686" t="n">
-        <v>0</v>
-      </c>
-      <c r="I686" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F687" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G687" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -25867,13 +25867,13 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F688" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G688" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -25904,13 +25904,13 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="F689" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="G689" t="n">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -25941,16 +25941,16 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F690" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G690" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H690" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I690" t="n">
         <v>1</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -25978,13 +25978,13 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="F691" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="G691" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -26006,28 +26006,28 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F692" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G692" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H692" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I692" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693">
@@ -26043,22 +26043,22 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F693" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="G693" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -26080,7 +26080,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -26089,13 +26089,13 @@
         </is>
       </c>
       <c r="E694" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F694" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G694" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -26117,7 +26117,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -26126,13 +26126,13 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F695" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G695" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -26163,13 +26163,13 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F696" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G696" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26191,28 +26191,28 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="F697" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="G697" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H697" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I697" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="698">
@@ -26228,22 +26228,22 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="G698" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -26265,7 +26265,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -26274,13 +26274,13 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F699" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G699" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -26297,12 +26297,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -26311,19 +26311,19 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F700" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G700" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H700" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="I700" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
@@ -26334,12 +26334,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -26348,19 +26348,19 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F701" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G701" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H701" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I701" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="702">
@@ -26376,28 +26376,28 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F702" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G702" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H702" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="I702" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="703">
@@ -26413,28 +26413,28 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H703" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="704">
@@ -26450,7 +26450,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -26459,13 +26459,13 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G704" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -26487,28 +26487,28 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F705" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G705" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H705" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I705" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706">
@@ -26524,28 +26524,28 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F706" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H706" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I706" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -26570,19 +26570,19 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="F707" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="G707" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H707" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I707" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="708">
@@ -26598,7 +26598,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -26607,19 +26607,19 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F708" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G708" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H708" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I708" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="709">
@@ -26635,7 +26635,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -26644,13 +26644,13 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="F709" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="G709" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -26672,12 +26672,12 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E710" t="n">
@@ -26709,28 +26709,28 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F711" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G711" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H711" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I711" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="712">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -26755,13 +26755,13 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F712" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G712" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -26783,12 +26783,12 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E713" t="n">
@@ -26801,10 +26801,10 @@
         <v>2</v>
       </c>
       <c r="H713" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I713" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="714">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E714" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F714" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G714" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -26857,7 +26857,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -26866,13 +26866,13 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F715" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G715" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -26889,12 +26889,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26903,13 +26903,13 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -26926,12 +26926,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -26940,19 +26940,19 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F717" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G717" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H717" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I717" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -26968,22 +26968,22 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -27023,10 +27023,10 @@
         <v>1</v>
       </c>
       <c r="H719" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
@@ -27042,22 +27042,22 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -27079,22 +27079,22 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F721" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -27116,28 +27116,28 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F722" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H722" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="I722" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="723">
@@ -27153,28 +27153,28 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F723" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G723" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H723" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I723" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -27199,19 +27199,19 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F724" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G724" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H724" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="I724" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="725">
@@ -27227,12 +27227,12 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E725" t="n">
@@ -27245,10 +27245,10 @@
         <v>1</v>
       </c>
       <c r="H725" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I725" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="726">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -27273,13 +27273,13 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F726" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G726" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -27301,12 +27301,12 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E727" t="n">
@@ -27319,10 +27319,10 @@
         <v>1</v>
       </c>
       <c r="H727" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I727" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
@@ -27338,22 +27338,22 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -27375,7 +27375,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -27393,9 +27393,83 @@
         <v>2</v>
       </c>
       <c r="H729" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I729" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>1</v>
+      </c>
+      <c r="F730" t="n">
+        <v>1</v>
+      </c>
+      <c r="G730" t="n">
+        <v>1</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>2</v>
+      </c>
+      <c r="F731" t="n">
+        <v>2</v>
+      </c>
+      <c r="G731" t="n">
+        <v>2</v>
+      </c>
+      <c r="H731" t="n">
+        <v>0</v>
+      </c>
+      <c r="I731" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F621" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G621" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H621" t="n">
         <v>908</v>
@@ -23795,13 +23795,13 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F632" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G632" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H632" t="n">
         <v>1159</v>
@@ -23980,13 +23980,13 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F637" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G637" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H637" t="n">
         <v>210</v>
@@ -24017,13 +24017,13 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F638" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G638" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H638" t="n">
         <v>1635</v>
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F645" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G645" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H645" t="n">
         <v>84</v>
@@ -24535,13 +24535,13 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F652" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G652" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H652" t="n">
         <v>389</v>
@@ -24868,13 +24868,13 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F661" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G661" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H661" t="n">
         <v>66</v>
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F686" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G686" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H686" t="n">
         <v>39</v>
@@ -25978,13 +25978,13 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F691" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G691" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -26237,13 +26237,13 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F698" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G698" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I726"/>
+  <dimension ref="A1:I727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F614" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G614" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="H614" t="n">
         <v>261</v>
@@ -23240,13 +23240,13 @@
         </is>
       </c>
       <c r="E617" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F617" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G617" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H617" t="n">
         <v>192</v>
@@ -23314,13 +23314,13 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F619" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G619" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H619" t="n">
         <v>324</v>
@@ -23425,13 +23425,13 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F622" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G622" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H622" t="n">
         <v>1119</v>
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F623" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G623" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="H623" t="n">
         <v>12651</v>
@@ -23499,13 +23499,13 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F624" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G624" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H624" t="n">
         <v>351</v>
@@ -23832,13 +23832,13 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F633" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G633" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H633" t="n">
         <v>6422</v>
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F635" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G635" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H635" t="n">
         <v>18351</v>
@@ -24017,13 +24017,13 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="F638" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="G638" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -24091,13 +24091,13 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F640" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G640" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -24128,13 +24128,13 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F641" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G641" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F643" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G643" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -24313,13 +24313,13 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F646" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G646" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H646" t="n">
         <v>299</v>
@@ -24350,13 +24350,13 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F647" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G647" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H647" t="n">
         <v>46</v>
@@ -24387,13 +24387,13 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F648" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G648" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -24424,13 +24424,13 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F649" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G649" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -24461,13 +24461,13 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F650" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G650" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H650" t="n">
         <v>339</v>
@@ -24683,13 +24683,13 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F656" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G656" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H656" t="n">
         <v>0</v>
@@ -24757,13 +24757,13 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F658" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G658" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H658" t="n">
         <v>14</v>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F659" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G659" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -24822,22 +24822,22 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F660" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G660" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H660" t="n">
         <v>0</v>
@@ -24859,28 +24859,28 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F661" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G661" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H661" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="I661" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662">
@@ -24901,23 +24901,23 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F662" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="G662" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="H662" t="n">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="I662" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="663">
@@ -24933,28 +24933,28 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="F663" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="G663" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H663" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="I663" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="664">
@@ -24975,17 +24975,17 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F664" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G664" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -25016,13 +25016,13 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F665" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G665" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -25044,28 +25044,28 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F666" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G666" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H666" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I666" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -25086,23 +25086,23 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F667" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G667" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H667" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -25118,28 +25118,28 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F668" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G668" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H668" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I668" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -25160,23 +25160,23 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F669" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G669" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H669" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I669" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="670">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -25201,19 +25201,19 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F670" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G670" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H670" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="I670" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="671">
@@ -25224,33 +25224,33 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="F671" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="G671" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="H671" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="I671" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="672">
@@ -25271,17 +25271,17 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="F672" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="G672" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -25303,22 +25303,22 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F673" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -25349,13 +25349,13 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F674" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G674" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -25377,7 +25377,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -25409,12 +25409,12 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -25423,13 +25423,13 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F676" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G676" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -25451,7 +25451,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -25460,13 +25460,13 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F677" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G677" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -25493,17 +25493,17 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F678" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G678" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -25525,28 +25525,28 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F679" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G679" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H679" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I679" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680">
@@ -25567,23 +25567,23 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F680" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G680" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H680" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I680" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -25599,22 +25599,22 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F681" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G681" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H681" t="n">
         <v>0</v>
@@ -25641,17 +25641,17 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F682" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G682" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H682" t="n">
         <v>0</v>
@@ -25673,28 +25673,28 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F683" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G683" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H683" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I683" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="684">
@@ -25715,23 +25715,23 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F684" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="G684" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="H684" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I684" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="685">
@@ -25747,28 +25747,28 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="F685" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G685" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="H685" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I685" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
@@ -25789,23 +25789,23 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F686" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G686" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H686" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I686" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="F687" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="G687" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H687" t="n">
         <v>0</v>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F688" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G688" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -25900,17 +25900,17 @@
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F689" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G689" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25932,28 +25932,28 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F690" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G690" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H690" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I690" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691">
@@ -25974,23 +25974,23 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F691" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G691" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="H691" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I691" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="692">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -26015,13 +26015,13 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F692" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="G692" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -26043,22 +26043,22 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F693" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G693" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -26085,17 +26085,17 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F694" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G694" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -26112,27 +26112,27 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F695" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G695" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -26159,17 +26159,17 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F696" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G696" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26191,22 +26191,22 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F697" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -26233,17 +26233,17 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F698" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G698" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -26265,22 +26265,22 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F699" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -26307,17 +26307,17 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -26339,22 +26339,22 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G701" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H701" t="n">
         <v>0</v>
@@ -26381,23 +26381,23 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F702" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G702" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H702" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I702" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="703">
@@ -26413,28 +26413,28 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F703" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G703" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H703" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I703" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="704">
@@ -26455,23 +26455,23 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F704" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="G704" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H704" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I704" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="705">
@@ -26487,22 +26487,22 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F705" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G705" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -26529,17 +26529,17 @@
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F706" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -26561,7 +26561,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -26570,13 +26570,13 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G707" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -26598,28 +26598,28 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F708" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G708" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H708" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I708" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="709">
@@ -26640,23 +26640,23 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F709" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G709" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H709" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="I709" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="710">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -26681,19 +26681,19 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F710" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G710" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H710" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I710" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="711">
@@ -26709,22 +26709,22 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -26751,17 +26751,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F712" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G712" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -26778,12 +26778,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -26792,13 +26792,13 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F713" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G713" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -26829,13 +26829,13 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F714" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G714" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -26857,12 +26857,12 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E715" t="n">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26903,13 +26903,13 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F716" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G716" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -26936,23 +26936,23 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F717" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G717" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H717" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="I717" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -26968,28 +26968,28 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G718" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H718" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="I718" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="719">
@@ -27010,17 +27010,17 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -27042,7 +27042,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -27051,19 +27051,19 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G720" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H720" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I720" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -27088,19 +27088,19 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H721" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I721" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="722">
@@ -27116,22 +27116,22 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F722" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G722" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -27158,17 +27158,17 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G723" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -27190,7 +27190,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -27199,19 +27199,19 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F724" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G724" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H724" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I724" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
@@ -27227,28 +27227,28 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F725" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G725" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H725" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I725" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="726">
@@ -27269,22 +27269,59 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E726" t="n">
+        <v>1</v>
+      </c>
+      <c r="F726" t="n">
+        <v>1</v>
+      </c>
+      <c r="G726" t="n">
+        <v>1</v>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
         <v>2</v>
       </c>
-      <c r="F726" t="n">
+      <c r="F727" t="n">
         <v>2</v>
       </c>
-      <c r="G726" t="n">
+      <c r="G727" t="n">
         <v>2</v>
       </c>
-      <c r="H726" t="n">
-        <v>0</v>
-      </c>
-      <c r="I726" t="n">
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+      <c r="I727" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I722"/>
+  <dimension ref="A1:I725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F330" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G330" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H330" t="n">
         <v>3507</v>
@@ -12917,13 +12917,13 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F338" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G338" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H338" t="n">
         <v>393</v>
@@ -16654,13 +16654,13 @@
         </is>
       </c>
       <c r="E439" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F439" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G439" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H439" t="n">
         <v>481</v>
@@ -16802,13 +16802,13 @@
         </is>
       </c>
       <c r="E443" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F443" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G443" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H443" t="n">
         <v>3862</v>
@@ -22944,13 +22944,13 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="F609" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G609" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H609" t="n">
         <v>261</v>
@@ -23018,13 +23018,13 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F611" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G611" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H611" t="n">
         <v>0</v>
@@ -23092,13 +23092,13 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F613" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G613" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H613" t="n">
         <v>46</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="E614" t="n">
+        <v>35</v>
+      </c>
+      <c r="F614" t="n">
+        <v>35</v>
+      </c>
+      <c r="G614" t="n">
         <v>36</v>
-      </c>
-      <c r="F614" t="n">
-        <v>37</v>
-      </c>
-      <c r="G614" t="n">
-        <v>38</v>
       </c>
       <c r="H614" t="n">
         <v>324</v>
@@ -23166,13 +23166,13 @@
         </is>
       </c>
       <c r="E615" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F615" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G615" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H615" t="n">
         <v>296</v>
@@ -23240,13 +23240,13 @@
         </is>
       </c>
       <c r="E617" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F617" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G617" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H617" t="n">
         <v>1119</v>
@@ -23280,10 +23280,10 @@
         <v>239</v>
       </c>
       <c r="F618" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G618" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H618" t="n">
         <v>12651</v>
@@ -23314,13 +23314,13 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F619" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G619" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H619" t="n">
         <v>351</v>
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F623" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G623" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -23536,13 +23536,13 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F625" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G625" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H625" t="n">
         <v>259</v>
@@ -23573,13 +23573,13 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F626" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G626" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H626" t="n">
         <v>1807</v>
@@ -23610,13 +23610,13 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -23684,13 +23684,13 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F629" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G629" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H629" t="n">
         <v>402</v>
@@ -23832,13 +23832,13 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F633" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="G633" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>
@@ -23906,13 +23906,13 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F635" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G635" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -24017,13 +24017,13 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F638" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G638" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -24128,13 +24128,13 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F641" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G641" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H641" t="n">
         <v>299</v>
@@ -24165,13 +24165,13 @@
         </is>
       </c>
       <c r="E642" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F642" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G642" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H642" t="n">
         <v>46</v>
@@ -24202,13 +24202,13 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F643" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G643" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -24387,13 +24387,13 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F648" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G648" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H648" t="n">
         <v>56</v>
@@ -24461,13 +24461,13 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H650" t="n">
         <v>0</v>
@@ -24609,13 +24609,13 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F654" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G654" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H654" t="n">
         <v>0</v>
@@ -24794,13 +24794,13 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F659" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G659" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H659" t="n">
         <v>0</v>
@@ -24979,13 +24979,13 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F664" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G664" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H664" t="n">
         <v>56</v>
@@ -25049,23 +25049,23 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F666" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G666" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H666" t="n">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="I666" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -25076,33 +25076,33 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="F667" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="G667" t="n">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="H667" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="I667" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="668">
@@ -25123,17 +25123,17 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="F668" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="G668" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -25155,22 +25155,22 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F669" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G669" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -25192,7 +25192,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -25201,13 +25201,13 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F670" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G670" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -25261,12 +25261,12 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -25275,13 +25275,13 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F672" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G672" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -25303,7 +25303,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -25312,13 +25312,13 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F673" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G673" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -25345,17 +25345,17 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F674" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G674" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H674" t="n">
         <v>0</v>
@@ -25377,28 +25377,28 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F675" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G675" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H675" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I675" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
@@ -25419,23 +25419,23 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F676" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G676" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H676" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I676" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="677">
@@ -25451,22 +25451,22 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F677" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G677" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -25493,17 +25493,17 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F678" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G678" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -25525,28 +25525,28 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="F679" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="G679" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H679" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I679" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680">
@@ -25567,23 +25567,23 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="F680" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="G680" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="H680" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I680" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="681">
@@ -25599,28 +25599,28 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="F681" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G681" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="H681" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I681" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="682">
@@ -25641,23 +25641,23 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F682" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G682" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H682" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I682" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -25682,13 +25682,13 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F683" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G683" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H683" t="n">
         <v>0</v>
@@ -25710,22 +25710,22 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F684" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G684" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -25752,17 +25752,17 @@
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F685" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G685" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -25784,28 +25784,28 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F686" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G686" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="H686" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I686" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -25826,23 +25826,23 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F687" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G687" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H687" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -25867,13 +25867,13 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="F688" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G688" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -25904,13 +25904,13 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F689" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G689" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25932,7 +25932,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -25941,13 +25941,13 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F690" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G690" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -26001,12 +26001,12 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -26015,13 +26015,13 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F692" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G692" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -26043,7 +26043,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -26117,7 +26117,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -26126,13 +26126,13 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F695" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G695" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -26154,7 +26154,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -26163,13 +26163,13 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G696" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -26200,13 +26200,13 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F697" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G697" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -26237,19 +26237,19 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G698" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H698" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I698" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="699">
@@ -26265,7 +26265,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -26274,19 +26274,19 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F699" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G699" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H699" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I699" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -26311,19 +26311,19 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F700" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="G700" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H700" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I700" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="701">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -26348,19 +26348,19 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F701" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G701" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H701" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I701" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702">
@@ -26376,7 +26376,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -26385,13 +26385,13 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="F702" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="G702" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -26413,12 +26413,12 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E703" t="n">
@@ -26450,28 +26450,28 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F704" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G704" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H704" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I704" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="705">
@@ -26487,7 +26487,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -26496,19 +26496,19 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F705" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G705" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H705" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I705" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706">
@@ -26524,28 +26524,28 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E706" t="n">
+        <v>6</v>
+      </c>
+      <c r="F706" t="n">
+        <v>6</v>
+      </c>
+      <c r="G706" t="n">
+        <v>6</v>
+      </c>
+      <c r="H706" t="n">
+        <v>44</v>
+      </c>
+      <c r="I706" t="n">
         <v>3</v>
-      </c>
-      <c r="F706" t="n">
-        <v>3</v>
-      </c>
-      <c r="G706" t="n">
-        <v>3</v>
-      </c>
-      <c r="H706" t="n">
-        <v>0</v>
-      </c>
-      <c r="I706" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -26561,28 +26561,28 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F707" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G707" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H707" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I707" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708">
@@ -26598,22 +26598,22 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F708" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G708" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -26630,12 +26630,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -26644,13 +26644,13 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F709" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G709" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -26667,27 +26667,27 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G710" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -26704,27 +26704,27 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F711" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G711" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -26746,22 +26746,22 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F712" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G712" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -26783,7 +26783,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -26792,19 +26792,19 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F713" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G713" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H713" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="I713" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -26857,22 +26857,22 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E715" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F715" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G715" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -26903,19 +26903,19 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F716" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G716" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H716" t="n">
-        <v>109</v>
+        <v>373</v>
       </c>
       <c r="I716" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="717">
@@ -26931,22 +26931,22 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -26968,22 +26968,22 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F718" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G718" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -27014,19 +27014,19 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G719" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H719" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I719" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="720">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -27051,19 +27051,19 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F720" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G720" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H720" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I720" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -27137,6 +27137,117 @@
         <v>0</v>
       </c>
       <c r="I722" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>3</v>
+      </c>
+      <c r="F723" t="n">
+        <v>3</v>
+      </c>
+      <c r="G723" t="n">
+        <v>3</v>
+      </c>
+      <c r="H723" t="n">
+        <v>90</v>
+      </c>
+      <c r="I723" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>1</v>
+      </c>
+      <c r="F724" t="n">
+        <v>1</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>3</v>
+      </c>
+      <c r="F725" t="n">
+        <v>3</v>
+      </c>
+      <c r="G725" t="n">
+        <v>3</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I725"/>
+  <dimension ref="A1:I726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19031,10 +19031,10 @@
         <v>885</v>
       </c>
       <c r="H503" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="I503" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="504">
@@ -19068,10 +19068,10 @@
         <v>14</v>
       </c>
       <c r="H504" t="n">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="I504" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="505">
@@ -19179,10 +19179,10 @@
         <v>23</v>
       </c>
       <c r="H507" t="n">
-        <v>839</v>
+        <v>1013</v>
       </c>
       <c r="I507" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="508">
@@ -19216,10 +19216,10 @@
         <v>15</v>
       </c>
       <c r="H508" t="n">
-        <v>9034</v>
+        <v>9203</v>
       </c>
       <c r="I508" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="509">
@@ -19253,10 +19253,10 @@
         <v>161</v>
       </c>
       <c r="H509" t="n">
-        <v>771</v>
+        <v>797</v>
       </c>
       <c r="I509" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="510">
@@ -19290,10 +19290,10 @@
         <v>132</v>
       </c>
       <c r="H510" t="n">
-        <v>7848</v>
+        <v>7881</v>
       </c>
       <c r="I510" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="511">
@@ -19660,10 +19660,10 @@
         <v>2</v>
       </c>
       <c r="H520" t="n">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="I520" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="521">
@@ -19697,10 +19697,10 @@
         <v>26</v>
       </c>
       <c r="H521" t="n">
-        <v>765</v>
+        <v>809</v>
       </c>
       <c r="I521" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="522">
@@ -19734,10 +19734,10 @@
         <v>29</v>
       </c>
       <c r="H522" t="n">
-        <v>7516</v>
+        <v>7603</v>
       </c>
       <c r="I522" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="523">
@@ -20733,10 +20733,10 @@
         <v>9</v>
       </c>
       <c r="H549" t="n">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="I549" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="550">
@@ -22879,10 +22879,10 @@
         <v>0</v>
       </c>
       <c r="H607" t="n">
-        <v>1458</v>
+        <v>1779</v>
       </c>
       <c r="I607" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="608">
@@ -22953,10 +22953,10 @@
         <v>72</v>
       </c>
       <c r="H609" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="I609" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="610">
@@ -23027,10 +23027,10 @@
         <v>34</v>
       </c>
       <c r="H611" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="612">
@@ -23064,10 +23064,10 @@
         <v>6</v>
       </c>
       <c r="H612" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="I612" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="613">
@@ -23101,10 +23101,10 @@
         <v>31</v>
       </c>
       <c r="H613" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="I613" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -23138,10 +23138,10 @@
         <v>36</v>
       </c>
       <c r="H614" t="n">
-        <v>324</v>
+        <v>525</v>
       </c>
       <c r="I614" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="615">
@@ -23212,10 +23212,10 @@
         <v>33</v>
       </c>
       <c r="H616" t="n">
-        <v>13886</v>
+        <v>19137</v>
       </c>
       <c r="I616" t="n">
-        <v>595</v>
+        <v>844</v>
       </c>
     </row>
     <row r="617">
@@ -23249,10 +23249,10 @@
         <v>136</v>
       </c>
       <c r="H617" t="n">
-        <v>1119</v>
+        <v>1864</v>
       </c>
       <c r="I617" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
     </row>
     <row r="618">
@@ -23286,10 +23286,10 @@
         <v>275</v>
       </c>
       <c r="H618" t="n">
-        <v>12651</v>
+        <v>18520</v>
       </c>
       <c r="I618" t="n">
-        <v>644</v>
+        <v>960</v>
       </c>
     </row>
     <row r="619">
@@ -23323,10 +23323,10 @@
         <v>62</v>
       </c>
       <c r="H619" t="n">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="I619" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="620">
@@ -23360,10 +23360,10 @@
         <v>57</v>
       </c>
       <c r="H620" t="n">
-        <v>1186</v>
+        <v>1349</v>
       </c>
       <c r="I620" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="621">
@@ -23397,10 +23397,10 @@
         <v>4</v>
       </c>
       <c r="H621" t="n">
-        <v>178</v>
+        <v>650</v>
       </c>
       <c r="I621" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="622">
@@ -23434,10 +23434,10 @@
         <v>12</v>
       </c>
       <c r="H622" t="n">
-        <v>645</v>
+        <v>955</v>
       </c>
       <c r="I622" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="623">
@@ -23545,10 +23545,10 @@
         <v>60</v>
       </c>
       <c r="H625" t="n">
-        <v>259</v>
+        <v>400</v>
       </c>
       <c r="I625" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="626">
@@ -23582,10 +23582,10 @@
         <v>83</v>
       </c>
       <c r="H626" t="n">
-        <v>1807</v>
+        <v>2383</v>
       </c>
       <c r="I626" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="627">
@@ -23656,10 +23656,10 @@
         <v>9</v>
       </c>
       <c r="H628" t="n">
-        <v>6422</v>
+        <v>7644</v>
       </c>
       <c r="I628" t="n">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="629">
@@ -23693,10 +23693,10 @@
         <v>24</v>
       </c>
       <c r="H629" t="n">
-        <v>402</v>
+        <v>476</v>
       </c>
       <c r="I629" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="630">
@@ -23730,10 +23730,10 @@
         <v>47</v>
       </c>
       <c r="H630" t="n">
-        <v>18351</v>
+        <v>23022</v>
       </c>
       <c r="I630" t="n">
-        <v>696</v>
+        <v>910</v>
       </c>
     </row>
     <row r="631">
@@ -23767,10 +23767,10 @@
         <v>0</v>
       </c>
       <c r="H631" t="n">
-        <v>2211</v>
+        <v>3710</v>
       </c>
       <c r="I631" t="n">
-        <v>94</v>
+        <v>161</v>
       </c>
     </row>
     <row r="632">
@@ -24063,10 +24063,10 @@
         <v>6</v>
       </c>
       <c r="H639" t="n">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="I639" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="640">
@@ -24100,10 +24100,10 @@
         <v>23</v>
       </c>
       <c r="H640" t="n">
-        <v>389</v>
+        <v>650</v>
       </c>
       <c r="I640" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="641">
@@ -24137,10 +24137,10 @@
         <v>68</v>
       </c>
       <c r="H641" t="n">
-        <v>299</v>
+        <v>548</v>
       </c>
       <c r="I641" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="642">
@@ -24174,10 +24174,10 @@
         <v>150</v>
       </c>
       <c r="H642" t="n">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="I642" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="643">
@@ -24285,10 +24285,10 @@
         <v>9</v>
       </c>
       <c r="H645" t="n">
-        <v>339</v>
+        <v>406</v>
       </c>
       <c r="I645" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="646">
@@ -24322,10 +24322,10 @@
         <v>12</v>
       </c>
       <c r="H646" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I646" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="647">
@@ -24396,10 +24396,10 @@
         <v>50</v>
       </c>
       <c r="H648" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="I648" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="649">
@@ -24544,10 +24544,10 @@
         <v>12</v>
       </c>
       <c r="H652" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="I652" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="653">
@@ -24581,10 +24581,10 @@
         <v>35</v>
       </c>
       <c r="H653" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="I653" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="654">
@@ -24729,10 +24729,10 @@
         <v>18</v>
       </c>
       <c r="H657" t="n">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="I657" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="658">
@@ -24766,10 +24766,10 @@
         <v>57</v>
       </c>
       <c r="H658" t="n">
-        <v>316</v>
+        <v>433</v>
       </c>
       <c r="I658" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="659">
@@ -24988,10 +24988,10 @@
         <v>3</v>
       </c>
       <c r="H664" t="n">
-        <v>56</v>
+        <v>313</v>
       </c>
       <c r="I664" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="665">
@@ -25099,10 +25099,10 @@
         <v>13</v>
       </c>
       <c r="H667" t="n">
-        <v>511</v>
+        <v>812</v>
       </c>
       <c r="I667" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="668">
@@ -25266,22 +25266,22 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H672" t="n">
         <v>0</v>
@@ -25298,12 +25298,12 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -25312,13 +25312,13 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F673" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G673" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -25349,19 +25349,19 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F674" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G674" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H674" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I674" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="675">
@@ -25382,17 +25382,17 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F675" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G675" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H675" t="n">
         <v>0</v>
@@ -25414,28 +25414,28 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F676" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G676" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H676" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I676" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="677">
@@ -25456,23 +25456,23 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F677" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G677" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H677" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I677" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="678">
@@ -25488,22 +25488,22 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="F678" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G678" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -25530,17 +25530,17 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F679" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G679" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -25562,28 +25562,28 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F680" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="G680" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="H680" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I680" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="681">
@@ -25604,23 +25604,23 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="F681" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="G681" t="n">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="H681" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I681" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="682">
@@ -25636,28 +25636,28 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="F682" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="G682" t="n">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="H682" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I682" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="683">
@@ -25678,23 +25678,23 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F683" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G683" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H683" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I683" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -25710,7 +25710,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -25719,13 +25719,13 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F684" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G684" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -25747,22 +25747,22 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F685" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G685" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H685" t="n">
         <v>0</v>
@@ -25789,17 +25789,17 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F686" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G686" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -25821,28 +25821,28 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F687" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G687" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H687" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I687" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -25863,23 +25863,23 @@
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="F688" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G688" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="H688" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I688" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
@@ -25895,22 +25895,22 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="F689" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="G689" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H689" t="n">
         <v>0</v>
@@ -25937,17 +25937,17 @@
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F690" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G690" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H690" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F691" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G691" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -26011,17 +26011,17 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F692" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G692" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H692" t="n">
         <v>0</v>
@@ -26038,27 +26038,27 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F693" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G693" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -26085,17 +26085,17 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -26117,22 +26117,22 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F695" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G695" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H695" t="n">
         <v>0</v>
@@ -26159,17 +26159,17 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F696" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G696" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -26191,22 +26191,22 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F697" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G697" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H697" t="n">
         <v>0</v>
@@ -26233,17 +26233,17 @@
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -26265,22 +26265,22 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F699" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G699" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H699" t="n">
         <v>0</v>
@@ -26307,23 +26307,23 @@
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F700" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G700" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H700" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I700" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="701">
@@ -26339,28 +26339,28 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F701" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G701" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H701" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I701" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="702">
@@ -26381,23 +26381,23 @@
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F702" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G702" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H702" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I702" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="703">
@@ -26413,28 +26413,28 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F703" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G703" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H703" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I703" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="704">
@@ -26455,17 +26455,17 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F704" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G704" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -26487,7 +26487,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -26496,13 +26496,13 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F705" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G705" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -26524,28 +26524,28 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F706" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G706" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H706" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I706" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
@@ -26566,23 +26566,23 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F707" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G707" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H707" t="n">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="I707" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="708">
@@ -26598,28 +26598,28 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F708" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G708" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H708" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I708" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="709">
@@ -26640,17 +26640,17 @@
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F709" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G709" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -26672,22 +26672,22 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -26714,17 +26714,17 @@
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F711" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G711" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -26741,12 +26741,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -26755,13 +26755,13 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F712" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G712" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H712" t="n">
         <v>0</v>
@@ -26783,7 +26783,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -26792,13 +26792,13 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -26820,12 +26820,12 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E714" t="n">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -26866,13 +26866,13 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F715" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G715" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -26899,23 +26899,23 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F716" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G716" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H716" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="I716" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="717">
@@ -26931,28 +26931,28 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F717" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G717" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H717" t="n">
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="I717" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="718">
@@ -26973,17 +26973,17 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G718" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H718" t="n">
         <v>0</v>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -27014,19 +27014,19 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F719" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G719" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H719" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="I719" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="720">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -27051,19 +27051,19 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G720" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H720" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="I720" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="721">
@@ -27079,22 +27079,22 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G721" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -27121,17 +27121,17 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F722" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G722" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -27171,10 +27171,10 @@
         <v>3</v>
       </c>
       <c r="H723" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I723" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="724">
@@ -27190,28 +27190,28 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F724" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G724" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H724" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="I724" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="725">
@@ -27232,22 +27232,59 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E725" t="n">
+        <v>1</v>
+      </c>
+      <c r="F725" t="n">
+        <v>1</v>
+      </c>
+      <c r="G725" t="n">
+        <v>1</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>£5K-£10K</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
         <v>3</v>
       </c>
-      <c r="F725" t="n">
+      <c r="F726" t="n">
         <v>3</v>
       </c>
-      <c r="G725" t="n">
+      <c r="G726" t="n">
         <v>3</v>
       </c>
-      <c r="H725" t="n">
-        <v>0</v>
-      </c>
-      <c r="I725" t="n">
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+      <c r="I726" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -23277,13 +23277,13 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F618" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G618" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H618" t="n">
         <v>18520</v>
@@ -23832,13 +23832,13 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F633" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G633" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H633" t="n">
         <v>0</v>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -16189,13 +16189,13 @@
         <v>45</v>
       </c>
       <c r="E541">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F541">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G541">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H541">
         <v>0</v>
@@ -16247,13 +16247,13 @@
         <v>45</v>
       </c>
       <c r="E543">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="F543">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="G543">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="H543">
         <v>415</v>
@@ -16305,13 +16305,13 @@
         <v>45</v>
       </c>
       <c r="E545">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F545">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G545">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H545">
         <v>481</v>
@@ -16595,13 +16595,13 @@
         <v>45</v>
       </c>
       <c r="E555">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F555">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G555">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H555">
         <v>346</v>
@@ -18654,13 +18654,13 @@
         <v>45</v>
       </c>
       <c r="E626">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F626">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G626">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H626">
         <v>0</v>
@@ -18712,13 +18712,13 @@
         <v>45</v>
       </c>
       <c r="E628">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F628">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="G628">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="H628">
         <v>245</v>
@@ -18770,13 +18770,13 @@
         <v>45</v>
       </c>
       <c r="E630">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F630">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G630">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H630">
         <v>185</v>
@@ -18886,13 +18886,13 @@
         <v>45</v>
       </c>
       <c r="E634">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F634">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G634">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H634">
         <v>598</v>
@@ -19118,13 +19118,13 @@
         <v>45</v>
       </c>
       <c r="E642">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F642">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G642">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H642">
         <v>238</v>
@@ -20510,13 +20510,13 @@
         <v>45</v>
       </c>
       <c r="E690">
+        <v>482</v>
+      </c>
+      <c r="F690">
         <v>485</v>
       </c>
-      <c r="F690">
-        <v>488</v>
-      </c>
       <c r="G690">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H690">
         <v>0</v>
@@ -20539,13 +20539,13 @@
         <v>45</v>
       </c>
       <c r="E691">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F691">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G691">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H691">
         <v>0</v>
@@ -22163,13 +22163,13 @@
         <v>45</v>
       </c>
       <c r="E747">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F747">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G747">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H747">
         <v>26</v>
@@ -22221,13 +22221,13 @@
         <v>45</v>
       </c>
       <c r="E749">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F749">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G749">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H749">
         <v>80</v>
@@ -22830,13 +22830,13 @@
         <v>45</v>
       </c>
       <c r="E770">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F770">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G770">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H770">
         <v>0</v>
@@ -22888,13 +22888,13 @@
         <v>45</v>
       </c>
       <c r="E772">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F772">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G772">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H772">
         <v>0</v>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I849"/>
+  <dimension ref="A1:I850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21288,10 +21288,10 @@
         <v>17</v>
       </c>
       <c r="H564" t="n">
-        <v>10048</v>
+        <v>10135</v>
       </c>
       <c r="I564" t="n">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="565">
@@ -21732,10 +21732,10 @@
         <v>2</v>
       </c>
       <c r="H576" t="n">
-        <v>754</v>
+        <v>773</v>
       </c>
       <c r="I576" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="577">
@@ -22953,10 +22953,10 @@
         <v>3</v>
       </c>
       <c r="H609" t="n">
-        <v>4601</v>
+        <v>4835</v>
       </c>
       <c r="I609" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="610">
@@ -24433,10 +24433,10 @@
         <v>32</v>
       </c>
       <c r="H649" t="n">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="I649" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="650">
@@ -25062,10 +25062,10 @@
         <v>6</v>
       </c>
       <c r="H666" t="n">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="I666" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="667">
@@ -25136,10 +25136,10 @@
         <v>35</v>
       </c>
       <c r="H668" t="n">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="I668" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="669">
@@ -25173,10 +25173,10 @@
         <v>13</v>
       </c>
       <c r="H669" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="I669" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="670">
@@ -25210,10 +25210,10 @@
         <v>32</v>
       </c>
       <c r="H670" t="n">
-        <v>17528</v>
+        <v>18710</v>
       </c>
       <c r="I670" t="n">
-        <v>777</v>
+        <v>827</v>
       </c>
     </row>
     <row r="671">
@@ -25247,10 +25247,10 @@
         <v>145</v>
       </c>
       <c r="H671" t="n">
-        <v>2607</v>
+        <v>2690</v>
       </c>
       <c r="I671" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="672">
@@ -25284,10 +25284,10 @@
         <v>278</v>
       </c>
       <c r="H672" t="n">
-        <v>19447</v>
+        <v>20351</v>
       </c>
       <c r="I672" t="n">
-        <v>996</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="673">
@@ -25321,10 +25321,10 @@
         <v>67</v>
       </c>
       <c r="H673" t="n">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="I673" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="674">
@@ -25358,10 +25358,10 @@
         <v>56</v>
       </c>
       <c r="H674" t="n">
-        <v>1342</v>
+        <v>1424</v>
       </c>
       <c r="I674" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="675">
@@ -25432,10 +25432,10 @@
         <v>12</v>
       </c>
       <c r="H676" t="n">
-        <v>5636</v>
+        <v>5743</v>
       </c>
       <c r="I676" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="677">
@@ -25543,10 +25543,10 @@
         <v>61</v>
       </c>
       <c r="H679" t="n">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="I679" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="680">
@@ -25657,7 +25657,7 @@
         <v>1761</v>
       </c>
       <c r="I682" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="683">
@@ -25728,10 +25728,10 @@
         <v>58</v>
       </c>
       <c r="H684" t="n">
-        <v>25438</v>
+        <v>26696</v>
       </c>
       <c r="I684" t="n">
-        <v>1014</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="685">
@@ -26061,10 +26061,10 @@
         <v>22</v>
       </c>
       <c r="H693" t="n">
-        <v>4854</v>
+        <v>4948</v>
       </c>
       <c r="I693" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="694">
@@ -26283,10 +26283,10 @@
         <v>10</v>
       </c>
       <c r="H699" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="I699" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="700">
@@ -26394,10 +26394,10 @@
         <v>50</v>
       </c>
       <c r="H702" t="n">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="I702" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="703">
@@ -26468,10 +26468,10 @@
         <v>2</v>
       </c>
       <c r="H704" t="n">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="I704" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="705">
@@ -26505,10 +26505,10 @@
         <v>7</v>
       </c>
       <c r="H705" t="n">
-        <v>3985</v>
+        <v>4024</v>
       </c>
       <c r="I705" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="706">
@@ -26542,10 +26542,10 @@
         <v>13</v>
       </c>
       <c r="H706" t="n">
-        <v>612</v>
+        <v>652</v>
       </c>
       <c r="I706" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="707">
@@ -26579,10 +26579,10 @@
         <v>38</v>
       </c>
       <c r="H707" t="n">
-        <v>500</v>
+        <v>586</v>
       </c>
       <c r="I707" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="708">
@@ -26949,10 +26949,10 @@
         <v>3</v>
       </c>
       <c r="H717" t="n">
-        <v>2262</v>
+        <v>2388</v>
       </c>
       <c r="I717" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="718">
@@ -27800,10 +27800,10 @@
         <v>3</v>
       </c>
       <c r="H740" t="n">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="I740" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="741">
@@ -27874,10 +27874,10 @@
         <v>46</v>
       </c>
       <c r="H742" t="n">
-        <v>578</v>
+        <v>901</v>
       </c>
       <c r="I742" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="743">
@@ -28577,10 +28577,10 @@
         <v>4</v>
       </c>
       <c r="H761" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="I761" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="762">
@@ -28799,10 +28799,10 @@
         <v>5</v>
       </c>
       <c r="H767" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I767" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="768">
@@ -28910,10 +28910,10 @@
         <v>3</v>
       </c>
       <c r="H770" t="n">
-        <v>2547</v>
+        <v>2717</v>
       </c>
       <c r="I770" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="771">
@@ -29206,10 +29206,10 @@
         <v>16</v>
       </c>
       <c r="H778" t="n">
-        <v>711</v>
+        <v>749</v>
       </c>
       <c r="I778" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="779">
@@ -29317,10 +29317,10 @@
         <v>1</v>
       </c>
       <c r="H781" t="n">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="I781" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="782">
@@ -29576,10 +29576,10 @@
         <v>1</v>
       </c>
       <c r="H788" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="I788" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="789">
@@ -29650,10 +29650,10 @@
         <v>4</v>
       </c>
       <c r="H790" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="I790" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="791">
@@ -29761,10 +29761,10 @@
         <v>2</v>
       </c>
       <c r="H793" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I793" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="794">
@@ -29798,10 +29798,10 @@
         <v>2</v>
       </c>
       <c r="H794" t="n">
-        <v>292</v>
+        <v>1683</v>
       </c>
       <c r="I794" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="795">
@@ -29872,10 +29872,10 @@
         <v>21</v>
       </c>
       <c r="H796" t="n">
-        <v>582</v>
+        <v>1171</v>
       </c>
       <c r="I796" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="797">
@@ -29946,10 +29946,10 @@
         <v>5</v>
       </c>
       <c r="H798" t="n">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="I798" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="799">
@@ -29983,10 +29983,10 @@
         <v>2</v>
       </c>
       <c r="H799" t="n">
-        <v>234</v>
+        <v>380</v>
       </c>
       <c r="I799" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="800">
@@ -30131,10 +30131,10 @@
         <v>5</v>
       </c>
       <c r="H803" t="n">
-        <v>294</v>
+        <v>467</v>
       </c>
       <c r="I803" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="804">
@@ -30168,10 +30168,10 @@
         <v>0</v>
       </c>
       <c r="H804" t="n">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="I804" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="805">
@@ -30242,10 +30242,10 @@
         <v>6</v>
       </c>
       <c r="H806" t="n">
-        <v>128</v>
+        <v>752</v>
       </c>
       <c r="I806" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="807">
@@ -30390,10 +30390,10 @@
         <v>6</v>
       </c>
       <c r="H810" t="n">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="I810" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="811">
@@ -30538,10 +30538,10 @@
         <v>0</v>
       </c>
       <c r="H814" t="n">
-        <v>1295</v>
+        <v>2050</v>
       </c>
       <c r="I814" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="815">
@@ -30612,10 +30612,10 @@
         <v>19</v>
       </c>
       <c r="H816" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="I816" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="817">
@@ -30982,10 +30982,10 @@
         <v>5</v>
       </c>
       <c r="H826" t="n">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="I826" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="827">
@@ -31056,10 +31056,10 @@
         <v>0</v>
       </c>
       <c r="H828" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I828" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="829">
@@ -31093,10 +31093,10 @@
         <v>0</v>
       </c>
       <c r="H829" t="n">
-        <v>260</v>
+        <v>425</v>
       </c>
       <c r="I829" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="830">
@@ -31181,33 +31181,33 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E832" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F832" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G832" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H832" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I832" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="833">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31260,22 +31260,22 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F834" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G834" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -31292,12 +31292,12 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -31306,13 +31306,13 @@
         </is>
       </c>
       <c r="E835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G835" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31389,10 +31389,10 @@
         <v>0</v>
       </c>
       <c r="H837" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I837" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="838">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -31417,19 +31417,19 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H838" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I838" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="839">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,13 +31491,13 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -31514,27 +31514,27 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -31561,7 +31561,7 @@
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E842" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E843" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F843" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G843" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -31630,22 +31630,22 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F844" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G844" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31676,19 +31676,19 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F845" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G845" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H845" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="I845" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31713,19 +31713,19 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F846" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G846" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H846" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="I846" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="847">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31750,16 +31750,16 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F847" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G847" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H847" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I847" t="n">
         <v>1</v>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31796,10 +31796,10 @@
         <v>0</v>
       </c>
       <c r="H848" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="849">
@@ -31815,27 +31815,64 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>0</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0</v>
+      </c>
+      <c r="G849" t="n">
+        <v>0</v>
+      </c>
+      <c r="H849" t="n">
+        <v>19</v>
+      </c>
+      <c r="I849" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
           <t>£50K+</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E849" t="n">
-        <v>0</v>
-      </c>
-      <c r="F849" t="n">
-        <v>0</v>
-      </c>
-      <c r="G849" t="n">
-        <v>0</v>
-      </c>
-      <c r="H849" t="n">
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>0</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G850" t="n">
+        <v>0</v>
+      </c>
+      <c r="H850" t="n">
         <v>53</v>
       </c>
-      <c r="I849" t="n">
+      <c r="I850" t="n">
         <v>2</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I850"/>
+  <dimension ref="A1:I851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F686" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G686" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H686" t="n">
         <v>0</v>
@@ -26024,10 +26024,10 @@
         <v>6</v>
       </c>
       <c r="H692" t="n">
-        <v>53</v>
+        <v>213</v>
       </c>
       <c r="I692" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="693">
@@ -26385,13 +26385,13 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F702" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G702" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H702" t="n">
         <v>173</v>
@@ -27800,10 +27800,10 @@
         <v>3</v>
       </c>
       <c r="H740" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I740" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="741">
@@ -29530,13 +29530,13 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F787" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G787" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H787" t="n">
         <v>0</v>
@@ -29604,13 +29604,13 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F789" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G789" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H789" t="n">
         <v>0</v>
@@ -30085,13 +30085,13 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F802" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G802" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -30316,10 +30316,10 @@
         <v>0</v>
       </c>
       <c r="H808" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I808" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="809">
@@ -30788,13 +30788,13 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F821" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G821" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -31334,22 +31334,22 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -31426,10 +31426,10 @@
         <v>0</v>
       </c>
       <c r="H838" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -31454,19 +31454,19 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F839" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H839" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I839" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="840">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31551,27 +31551,27 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -31598,7 +31598,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E843" t="n">
@@ -31630,22 +31630,22 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E844" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G844" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -31667,22 +31667,22 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E845" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F845" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G845" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H845" t="n">
         <v>0</v>
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31713,19 +31713,19 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F846" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G846" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H846" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="I846" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="847">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -31750,19 +31750,19 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G847" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H847" t="n">
-        <v>10</v>
+        <v>584</v>
       </c>
       <c r="I847" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="848">
@@ -31773,12 +31773,12 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -31787,19 +31787,19 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H848" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I848" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="849">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -31833,10 +31833,10 @@
         <v>0</v>
       </c>
       <c r="H849" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I849" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="850">
@@ -31852,27 +31852,64 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>0</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G850" t="n">
+        <v>0</v>
+      </c>
+      <c r="H850" t="n">
+        <v>19</v>
+      </c>
+      <c r="I850" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
           <t>£50K+</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E850" t="n">
-        <v>0</v>
-      </c>
-      <c r="F850" t="n">
-        <v>0</v>
-      </c>
-      <c r="G850" t="n">
-        <v>0</v>
-      </c>
-      <c r="H850" t="n">
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>0</v>
+      </c>
+      <c r="F851" t="n">
+        <v>0</v>
+      </c>
+      <c r="G851" t="n">
+        <v>0</v>
+      </c>
+      <c r="H851" t="n">
         <v>53</v>
       </c>
-      <c r="I850" t="n">
+      <c r="I851" t="n">
         <v>2</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I844"/>
+  <dimension ref="A1:I846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,10 +20548,10 @@
         <v>128</v>
       </c>
       <c r="H544" t="n">
-        <v>6366</v>
+        <v>6376</v>
       </c>
       <c r="I544" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="545">
@@ -20696,10 +20696,10 @@
         <v>6</v>
       </c>
       <c r="H548" t="n">
-        <v>6716</v>
+        <v>6748</v>
       </c>
       <c r="I548" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="549">
@@ -20992,10 +20992,10 @@
         <v>26</v>
       </c>
       <c r="H556" t="n">
-        <v>7359</v>
+        <v>7379</v>
       </c>
       <c r="I556" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="557">
@@ -22611,13 +22611,13 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F600" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G600" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -22648,13 +22648,13 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F601" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G601" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -24137,10 +24137,10 @@
         <v>1</v>
       </c>
       <c r="H641" t="n">
-        <v>4895</v>
+        <v>4914</v>
       </c>
       <c r="I641" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="642">
@@ -24766,10 +24766,10 @@
         <v>31</v>
       </c>
       <c r="H658" t="n">
-        <v>9754</v>
+        <v>10192</v>
       </c>
       <c r="I658" t="n">
-        <v>409</v>
+        <v>423</v>
       </c>
     </row>
     <row r="659">
@@ -24803,10 +24803,10 @@
         <v>145</v>
       </c>
       <c r="H659" t="n">
-        <v>2687</v>
+        <v>2750</v>
       </c>
       <c r="I659" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="660">
@@ -24840,10 +24840,10 @@
         <v>277</v>
       </c>
       <c r="H660" t="n">
-        <v>19848</v>
+        <v>20224</v>
       </c>
       <c r="I660" t="n">
-        <v>1023</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="661">
@@ -24877,10 +24877,10 @@
         <v>68</v>
       </c>
       <c r="H661" t="n">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="I661" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="662">
@@ -24988,10 +24988,10 @@
         <v>13</v>
       </c>
       <c r="H664" t="n">
-        <v>14846</v>
+        <v>15109</v>
       </c>
       <c r="I664" t="n">
-        <v>682</v>
+        <v>695</v>
       </c>
     </row>
     <row r="665">
@@ -25210,10 +25210,10 @@
         <v>9</v>
       </c>
       <c r="H670" t="n">
-        <v>4465</v>
+        <v>4526</v>
       </c>
       <c r="I670" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="671">
@@ -25284,10 +25284,10 @@
         <v>59</v>
       </c>
       <c r="H672" t="n">
-        <v>28102</v>
+        <v>28737</v>
       </c>
       <c r="I672" t="n">
-        <v>1130</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="673">
@@ -25617,10 +25617,10 @@
         <v>23</v>
       </c>
       <c r="H681" t="n">
-        <v>5284</v>
+        <v>5338</v>
       </c>
       <c r="I681" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="682">
@@ -25950,10 +25950,10 @@
         <v>50</v>
       </c>
       <c r="H690" t="n">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="I690" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="691">
@@ -26061,10 +26061,10 @@
         <v>7</v>
       </c>
       <c r="H693" t="n">
-        <v>4057</v>
+        <v>4076</v>
       </c>
       <c r="I693" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="694">
@@ -26394,10 +26394,10 @@
         <v>54</v>
       </c>
       <c r="H702" t="n">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="I702" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="703">
@@ -27393,10 +27393,10 @@
         <v>46</v>
       </c>
       <c r="H729" t="n">
-        <v>921</v>
+        <v>1007</v>
       </c>
       <c r="I729" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="730">
@@ -28873,10 +28873,10 @@
         <v>1</v>
       </c>
       <c r="H769" t="n">
-        <v>2229</v>
+        <v>2246</v>
       </c>
       <c r="I769" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="770">
@@ -29132,10 +29132,10 @@
         <v>42</v>
       </c>
       <c r="H776" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="I776" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="777">
@@ -29169,10 +29169,10 @@
         <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I777" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="778">
@@ -29243,10 +29243,10 @@
         <v>4</v>
       </c>
       <c r="H779" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="I779" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="780">
@@ -29280,10 +29280,10 @@
         <v>4</v>
       </c>
       <c r="H780" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I780" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="781">
@@ -29354,10 +29354,10 @@
         <v>3</v>
       </c>
       <c r="H782" t="n">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="I782" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="783">
@@ -29391,10 +29391,10 @@
         <v>2</v>
       </c>
       <c r="H783" t="n">
-        <v>1546</v>
+        <v>1671</v>
       </c>
       <c r="I783" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="784">
@@ -29428,10 +29428,10 @@
         <v>10</v>
       </c>
       <c r="H784" t="n">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="I784" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="785">
@@ -29465,10 +29465,10 @@
         <v>26</v>
       </c>
       <c r="H785" t="n">
-        <v>1430</v>
+        <v>1527</v>
       </c>
       <c r="I785" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="786">
@@ -29576,10 +29576,10 @@
         <v>3</v>
       </c>
       <c r="H788" t="n">
-        <v>993</v>
+        <v>1215</v>
       </c>
       <c r="I788" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="789">
@@ -29724,10 +29724,10 @@
         <v>6</v>
       </c>
       <c r="H792" t="n">
-        <v>529</v>
+        <v>565</v>
       </c>
       <c r="I792" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="793">
@@ -29761,10 +29761,10 @@
         <v>0</v>
       </c>
       <c r="H793" t="n">
-        <v>1228</v>
+        <v>1518</v>
       </c>
       <c r="I793" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="794">
@@ -29835,10 +29835,10 @@
         <v>7</v>
       </c>
       <c r="H795" t="n">
-        <v>891</v>
+        <v>1012</v>
       </c>
       <c r="I795" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="796">
@@ -29863,13 +29863,13 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F796" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G796" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -29900,13 +29900,13 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G797" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H797" t="n">
         <v>0</v>
@@ -29937,13 +29937,13 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F798" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G798" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H798" t="n">
         <v>0</v>
@@ -29974,19 +29974,19 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F799" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G799" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H799" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="I799" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="800">
@@ -30131,10 +30131,10 @@
         <v>6</v>
       </c>
       <c r="H803" t="n">
-        <v>2325</v>
+        <v>2672</v>
       </c>
       <c r="I803" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="804">
@@ -30205,10 +30205,10 @@
         <v>27</v>
       </c>
       <c r="H805" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="I805" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="806">
@@ -30279,10 +30279,10 @@
         <v>4</v>
       </c>
       <c r="H807" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="I807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="808">
@@ -30464,10 +30464,10 @@
         <v>13</v>
       </c>
       <c r="H812" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I812" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="813">
@@ -30575,10 +30575,10 @@
         <v>10</v>
       </c>
       <c r="H815" t="n">
-        <v>377</v>
+        <v>490</v>
       </c>
       <c r="I815" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="816">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Lemon Ginger</t>
+          <t>Hibiscus</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -30742,7 +30742,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -30760,10 +30760,10 @@
         <v>0</v>
       </c>
       <c r="H820" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I820" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="821">
@@ -30774,33 +30774,33 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Lemon Ginger</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H821" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I821" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="822">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -30853,12 +30853,12 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E823" t="n">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -30899,13 +30899,13 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F824" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G824" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -30922,12 +30922,12 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Psyllium Fiber</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -30936,19 +30936,19 @@
         </is>
       </c>
       <c r="E825" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F825" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G825" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H825" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="I825" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="826">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -30973,19 +30973,19 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F826" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G826" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H826" t="n">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="I826" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="827">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -31019,10 +31019,10 @@
         <v>0</v>
       </c>
       <c r="H827" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="I827" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="828">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -31047,19 +31047,19 @@
         </is>
       </c>
       <c r="E828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H828" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="I828" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="829">
@@ -31075,7 +31075,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -31084,13 +31084,13 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G829" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31149,7 +31149,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -31167,10 +31167,10 @@
         <v>0</v>
       </c>
       <c r="H831" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I831" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="832">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -31204,10 +31204,10 @@
         <v>0</v>
       </c>
       <c r="H832" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I832" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="833">
@@ -31218,27 +31218,27 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E833" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F833" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G833" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -31265,17 +31265,17 @@
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -31297,22 +31297,22 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E835" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F835" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G835" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31334,22 +31334,22 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E836" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F836" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G836" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -31380,13 +31380,13 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F837" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G837" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -31408,22 +31408,22 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E838" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F838" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G838" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -31445,28 +31445,28 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F839" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G839" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I839" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="840">
@@ -31477,12 +31477,12 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -31491,19 +31491,19 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F840" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G840" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H840" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I840" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="841">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31574,10 +31574,10 @@
         <v>0</v>
       </c>
       <c r="H842" t="n">
-        <v>625</v>
+        <v>19</v>
       </c>
       <c r="I842" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="843">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31611,10 +31611,10 @@
         <v>0</v>
       </c>
       <c r="H843" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="I843" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="844">
@@ -31630,27 +31630,101 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>0</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0</v>
+      </c>
+      <c r="G844" t="n">
+        <v>0</v>
+      </c>
+      <c r="H844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>0</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0</v>
+      </c>
+      <c r="G845" t="n">
+        <v>0</v>
+      </c>
+      <c r="H845" t="n">
+        <v>82</v>
+      </c>
+      <c r="I845" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E844" t="n">
-        <v>1</v>
-      </c>
-      <c r="F844" t="n">
-        <v>1</v>
-      </c>
-      <c r="G844" t="n">
-        <v>1</v>
-      </c>
-      <c r="H844" t="n">
-        <v>0</v>
-      </c>
-      <c r="I844" t="n">
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>1</v>
+      </c>
+      <c r="F846" t="n">
+        <v>1</v>
+      </c>
+      <c r="G846" t="n">
+        <v>1</v>
+      </c>
+      <c r="H846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I846"/>
+  <dimension ref="A1:I847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,10 +20548,10 @@
         <v>128</v>
       </c>
       <c r="H544" t="n">
-        <v>6376</v>
+        <v>6389</v>
       </c>
       <c r="I544" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="545">
@@ -20696,10 +20696,10 @@
         <v>6</v>
       </c>
       <c r="H548" t="n">
-        <v>6748</v>
+        <v>6806</v>
       </c>
       <c r="I548" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="549">
@@ -20955,10 +20955,10 @@
         <v>28</v>
       </c>
       <c r="H555" t="n">
-        <v>1158</v>
+        <v>1235</v>
       </c>
       <c r="I555" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="556">
@@ -20992,10 +20992,10 @@
         <v>26</v>
       </c>
       <c r="H556" t="n">
-        <v>7379</v>
+        <v>7389</v>
       </c>
       <c r="I556" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="557">
@@ -24766,10 +24766,10 @@
         <v>31</v>
       </c>
       <c r="H658" t="n">
-        <v>10192</v>
+        <v>10482</v>
       </c>
       <c r="I658" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="659">
@@ -24803,10 +24803,10 @@
         <v>145</v>
       </c>
       <c r="H659" t="n">
-        <v>2750</v>
+        <v>2760</v>
       </c>
       <c r="I659" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="660">
@@ -24840,10 +24840,10 @@
         <v>277</v>
       </c>
       <c r="H660" t="n">
-        <v>20224</v>
+        <v>20622</v>
       </c>
       <c r="I660" t="n">
-        <v>1041</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="661">
@@ -24951,10 +24951,10 @@
         <v>4</v>
       </c>
       <c r="H663" t="n">
-        <v>749</v>
+        <v>792</v>
       </c>
       <c r="I663" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="664">
@@ -24988,10 +24988,10 @@
         <v>13</v>
       </c>
       <c r="H664" t="n">
-        <v>15109</v>
+        <v>15341</v>
       </c>
       <c r="I664" t="n">
-        <v>695</v>
+        <v>705</v>
       </c>
     </row>
     <row r="665">
@@ -25210,10 +25210,10 @@
         <v>9</v>
       </c>
       <c r="H670" t="n">
-        <v>4526</v>
+        <v>4545</v>
       </c>
       <c r="I670" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="671">
@@ -25284,10 +25284,10 @@
         <v>59</v>
       </c>
       <c r="H672" t="n">
-        <v>28737</v>
+        <v>29106</v>
       </c>
       <c r="I672" t="n">
-        <v>1155</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="673">
@@ -25617,10 +25617,10 @@
         <v>23</v>
       </c>
       <c r="H681" t="n">
-        <v>5338</v>
+        <v>5419</v>
       </c>
       <c r="I681" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="682">
@@ -25839,10 +25839,10 @@
         <v>10</v>
       </c>
       <c r="H687" t="n">
-        <v>507</v>
+        <v>560</v>
       </c>
       <c r="I687" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="688">
@@ -26024,10 +26024,10 @@
         <v>2</v>
       </c>
       <c r="H692" t="n">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="I692" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="693">
@@ -26061,10 +26061,10 @@
         <v>7</v>
       </c>
       <c r="H693" t="n">
-        <v>4076</v>
+        <v>4095</v>
       </c>
       <c r="I693" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="694">
@@ -27393,10 +27393,10 @@
         <v>46</v>
       </c>
       <c r="H729" t="n">
-        <v>1007</v>
+        <v>1051</v>
       </c>
       <c r="I729" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="730">
@@ -28873,10 +28873,10 @@
         <v>1</v>
       </c>
       <c r="H769" t="n">
-        <v>2246</v>
+        <v>2288</v>
       </c>
       <c r="I769" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="770">
@@ -29123,13 +29123,13 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F776" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G776" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H776" t="n">
         <v>88</v>
@@ -29169,10 +29169,10 @@
         <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="I777" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="778">
@@ -29200,10 +29200,10 @@
         <v>28</v>
       </c>
       <c r="F778" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G778" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H778" t="n">
         <v>0</v>
@@ -29354,10 +29354,10 @@
         <v>3</v>
       </c>
       <c r="H782" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="I782" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="783">
@@ -29391,10 +29391,10 @@
         <v>2</v>
       </c>
       <c r="H783" t="n">
-        <v>1671</v>
+        <v>2165</v>
       </c>
       <c r="I783" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="784">
@@ -29465,10 +29465,10 @@
         <v>26</v>
       </c>
       <c r="H785" t="n">
-        <v>1527</v>
+        <v>2050</v>
       </c>
       <c r="I785" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="786">
@@ -29502,10 +29502,10 @@
         <v>7</v>
       </c>
       <c r="H786" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I786" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="787">
@@ -29530,19 +29530,19 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F787" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G787" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H787" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="I787" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="788">
@@ -29576,10 +29576,10 @@
         <v>3</v>
       </c>
       <c r="H788" t="n">
-        <v>1215</v>
+        <v>1550</v>
       </c>
       <c r="I788" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="789">
@@ -29724,10 +29724,10 @@
         <v>6</v>
       </c>
       <c r="H792" t="n">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="I792" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="793">
@@ -29761,10 +29761,10 @@
         <v>0</v>
       </c>
       <c r="H793" t="n">
-        <v>1518</v>
+        <v>1796</v>
       </c>
       <c r="I793" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="794">
@@ -29835,10 +29835,10 @@
         <v>7</v>
       </c>
       <c r="H795" t="n">
-        <v>1012</v>
+        <v>1166</v>
       </c>
       <c r="I795" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="796">
@@ -29863,13 +29863,13 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F796" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G796" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -30131,10 +30131,10 @@
         <v>6</v>
       </c>
       <c r="H803" t="n">
-        <v>2672</v>
+        <v>2961</v>
       </c>
       <c r="I803" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="804">
@@ -30205,10 +30205,10 @@
         <v>27</v>
       </c>
       <c r="H805" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="I805" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="806">
@@ -30464,10 +30464,10 @@
         <v>13</v>
       </c>
       <c r="H812" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I812" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="813">
@@ -30501,10 +30501,10 @@
         <v>2</v>
       </c>
       <c r="H813" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="I813" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="814">
@@ -30575,10 +30575,10 @@
         <v>10</v>
       </c>
       <c r="H815" t="n">
-        <v>490</v>
+        <v>623</v>
       </c>
       <c r="I815" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="816">
@@ -30982,10 +30982,10 @@
         <v>1</v>
       </c>
       <c r="H826" t="n">
-        <v>711</v>
+        <v>828</v>
       </c>
       <c r="I826" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="827">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31574,10 +31574,10 @@
         <v>0</v>
       </c>
       <c r="H842" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="843">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31611,10 +31611,10 @@
         <v>0</v>
       </c>
       <c r="H843" t="n">
-        <v>758</v>
+        <v>94</v>
       </c>
       <c r="I843" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="844">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -31648,10 +31648,10 @@
         <v>0</v>
       </c>
       <c r="H844" t="n">
-        <v>0</v>
+        <v>933</v>
       </c>
       <c r="I844" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="845">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31685,10 +31685,10 @@
         <v>0</v>
       </c>
       <c r="H845" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I845" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -31704,27 +31704,64 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>0</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0</v>
+      </c>
+      <c r="G846" t="n">
+        <v>0</v>
+      </c>
+      <c r="H846" t="n">
+        <v>125</v>
+      </c>
+      <c r="I846" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E846" t="n">
-        <v>1</v>
-      </c>
-      <c r="F846" t="n">
-        <v>1</v>
-      </c>
-      <c r="G846" t="n">
-        <v>1</v>
-      </c>
-      <c r="H846" t="n">
-        <v>0</v>
-      </c>
-      <c r="I846" t="n">
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>1</v>
+      </c>
+      <c r="F847" t="n">
+        <v>1</v>
+      </c>
+      <c r="G847" t="n">
+        <v>1</v>
+      </c>
+      <c r="H847" t="n">
+        <v>0</v>
+      </c>
+      <c r="I847" t="n">
         <v>0</v>
       </c>
     </row>

--- a/segment_product_slab.xlsx
+++ b/segment_product_slab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I847"/>
+  <dimension ref="A1:I848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,10 +20548,10 @@
         <v>128</v>
       </c>
       <c r="H544" t="n">
-        <v>6389</v>
+        <v>6402</v>
       </c>
       <c r="I544" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="545">
@@ -20807,10 +20807,10 @@
         <v>161</v>
       </c>
       <c r="H551" t="n">
-        <v>238</v>
+        <v>290</v>
       </c>
       <c r="I551" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="552">
@@ -20918,10 +20918,10 @@
         <v>2</v>
       </c>
       <c r="H554" t="n">
-        <v>930</v>
+        <v>949</v>
       </c>
       <c r="I554" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="555">
@@ -24140,7 +24140,7 @@
         <v>4914</v>
       </c>
       <c r="I641" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="642">
@@ -24544,10 +24544,10 @@
         <v>7</v>
       </c>
       <c r="H652" t="n">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="I652" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="653">
@@ -24692,10 +24692,10 @@
         <v>35</v>
       </c>
       <c r="H656" t="n">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="I656" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="657">
@@ -24766,10 +24766,10 @@
         <v>31</v>
       </c>
       <c r="H658" t="n">
-        <v>10482</v>
+        <v>10976</v>
       </c>
       <c r="I658" t="n">
-        <v>428</v>
+        <v>445</v>
       </c>
     </row>
     <row r="659">
@@ -24803,10 +24803,10 @@
         <v>145</v>
       </c>
       <c r="H659" t="n">
-        <v>2760</v>
+        <v>2800</v>
       </c>
       <c r="I659" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="660">
@@ -24840,10 +24840,10 @@
         <v>277</v>
       </c>
       <c r="H660" t="n">
-        <v>20622</v>
+        <v>20765</v>
       </c>
       <c r="I660" t="n">
-        <v>1054</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="661">
@@ -24988,10 +24988,10 @@
         <v>13</v>
       </c>
       <c r="H664" t="n">
-        <v>15341</v>
+        <v>15567</v>
       </c>
       <c r="I664" t="n">
-        <v>705</v>
+        <v>717</v>
       </c>
     </row>
     <row r="665">
@@ -25102,7 +25102,7 @@
         <v>487</v>
       </c>
       <c r="I667" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="668">
@@ -25210,10 +25210,10 @@
         <v>9</v>
       </c>
       <c r="H670" t="n">
-        <v>4545</v>
+        <v>4638</v>
       </c>
       <c r="I670" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="671">
@@ -25284,10 +25284,10 @@
         <v>59</v>
       </c>
       <c r="H672" t="n">
-        <v>29106</v>
+        <v>29540</v>
       </c>
       <c r="I672" t="n">
-        <v>1169</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="673">
@@ -25617,10 +25617,10 @@
         <v>23</v>
       </c>
       <c r="H681" t="n">
-        <v>5419</v>
+        <v>5454</v>
       </c>
       <c r="I681" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="682">
@@ -25839,10 +25839,10 @@
         <v>10</v>
       </c>
       <c r="H687" t="n">
-        <v>560</v>
+        <v>683</v>
       </c>
       <c r="I687" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="688">
@@ -25876,10 +25876,10 @@
         <v>13</v>
       </c>
       <c r="H688" t="n">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="I688" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="689">
@@ -28096,10 +28096,10 @@
         <v>5</v>
       </c>
       <c r="H748" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I748" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="749">
@@ -28281,10 +28281,10 @@
         <v>2</v>
       </c>
       <c r="H753" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="I753" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="754">
@@ -29169,10 +29169,10 @@
         <v>1</v>
       </c>
       <c r="H777" t="n">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="I777" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="778">
@@ -29243,10 +29243,10 @@
         <v>4</v>
       </c>
       <c r="H779" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="I779" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="780">
@@ -29317,10 +29317,10 @@
         <v>1</v>
       </c>
       <c r="H781" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I781" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="782">
@@ -29391,10 +29391,10 @@
         <v>2</v>
       </c>
       <c r="H783" t="n">
-        <v>2165</v>
+        <v>2237</v>
       </c>
       <c r="I783" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="784">
@@ -29428,10 +29428,10 @@
         <v>10</v>
       </c>
       <c r="H784" t="n">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="I784" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="785">
@@ -29465,10 +29465,10 @@
         <v>26</v>
       </c>
       <c r="H785" t="n">
-        <v>2050</v>
+        <v>2281</v>
       </c>
       <c r="I785" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="786">
@@ -29539,10 +29539,10 @@
         <v>7</v>
       </c>
       <c r="H787" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="I787" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="788">
@@ -29576,10 +29576,10 @@
         <v>3</v>
       </c>
       <c r="H788" t="n">
-        <v>1550</v>
+        <v>1715</v>
       </c>
       <c r="I788" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="789">
@@ -29727,7 +29727,7 @@
         <v>632</v>
       </c>
       <c r="I792" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="793">
@@ -29761,10 +29761,10 @@
         <v>0</v>
       </c>
       <c r="H793" t="n">
-        <v>1796</v>
+        <v>2050</v>
       </c>
       <c r="I793" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="794">
@@ -29835,10 +29835,10 @@
         <v>7</v>
       </c>
       <c r="H795" t="n">
-        <v>1166</v>
+        <v>1389</v>
       </c>
       <c r="I795" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="796">
@@ -30131,10 +30131,10 @@
         <v>6</v>
       </c>
       <c r="H803" t="n">
-        <v>2961</v>
+        <v>3303</v>
       </c>
       <c r="I803" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="804">
@@ -30205,10 +30205,10 @@
         <v>27</v>
       </c>
       <c r="H805" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="I805" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="806">
@@ -30316,10 +30316,10 @@
         <v>1</v>
       </c>
       <c r="H808" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="I808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -30575,10 +30575,10 @@
         <v>10</v>
       </c>
       <c r="H815" t="n">
-        <v>623</v>
+        <v>677</v>
       </c>
       <c r="I815" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="816">
@@ -30982,10 +30982,10 @@
         <v>1</v>
       </c>
       <c r="H826" t="n">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="I826" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="827">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -31056,10 +31056,10 @@
         <v>0</v>
       </c>
       <c r="H828" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="I828" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829">
@@ -31075,7 +31075,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -31084,19 +31084,19 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H829" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="I829" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="830">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>£50-£100</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -31121,13 +31121,13 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G830" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -31149,7 +31149,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£50-£100</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -31204,10 +31204,10 @@
         <v>0</v>
       </c>
       <c r="H832" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I832" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -31241,10 +31241,10 @@
         <v>0</v>
       </c>
       <c r="H833" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I833" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="834">
@@ -31255,27 +31255,27 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Spearmint</t>
+          <t>Psyllium Fiber</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E834" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F834" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G834" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -31302,17 +31302,17 @@
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E835" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F835" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G835" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -31334,22 +31334,22 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>£0-£50</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E836" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F836" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G836" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -31371,22 +31371,22 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>£100-£200</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E837" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F837" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G837" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -31408,7 +31408,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -31417,13 +31417,13 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F838" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G838" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -31445,22 +31445,22 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="E839" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F839" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -31482,28 +31482,28 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£50K+</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>New</t>
         </is>
       </c>
       <c r="E840" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F840" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G840" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H840" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I840" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="841">
@@ -31514,12 +31514,12 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Turmeric Curcumin</t>
+          <t>Spearmint</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
@@ -31528,19 +31528,19 @@
         </is>
       </c>
       <c r="E841" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F841" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G841" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H841" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I841" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="842">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>No data</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -31611,10 +31611,10 @@
         <v>0</v>
       </c>
       <c r="H843" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I843" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="844">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -31648,10 +31648,10 @@
         <v>0</v>
       </c>
       <c r="H844" t="n">
-        <v>933</v>
+        <v>94</v>
       </c>
       <c r="I844" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="845">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -31685,10 +31685,10 @@
         <v>0</v>
       </c>
       <c r="H845" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="I845" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="846">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -31722,10 +31722,10 @@
         <v>0</v>
       </c>
       <c r="H846" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I846" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="847">
@@ -31741,27 +31741,64 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>0</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0</v>
+      </c>
+      <c r="G847" t="n">
+        <v>0</v>
+      </c>
+      <c r="H847" t="n">
+        <v>125</v>
+      </c>
+      <c r="I847" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Turmeric Curcumin</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
           <t>£5K-£10K</t>
         </is>
       </c>
-      <c r="D847" t="inlineStr">
-        <is>
-          <t>Old</t>
-        </is>
-      </c>
-      <c r="E847" t="n">
-        <v>1</v>
-      </c>
-      <c r="F847" t="n">
-        <v>1</v>
-      </c>
-      <c r="G847" t="n">
-        <v>1</v>
-      </c>
-      <c r="H847" t="n">
-        <v>0</v>
-      </c>
-      <c r="I847" t="n">
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>1</v>
+      </c>
+      <c r="F848" t="n">
+        <v>1</v>
+      </c>
+      <c r="G848" t="n">
+        <v>1</v>
+      </c>
+      <c r="H848" t="n">
+        <v>0</v>
+      </c>
+      <c r="I848" t="n">
         <v>0</v>
       </c>
     </row>
